--- a/client/dist/Sorce/balanceDP.xlsx
+++ b/client/dist/Sorce/balanceDP.xlsx
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/SharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="452">
   <si>
     <t>Формирвоание отчета</t>
   </si>
   <si>
-    <t>Период: на 23.12.2025 16:15:13</t>
+    <t>Период: на 23.02.2026 11:15:12</t>
   </si>
   <si>
     <t>Показатели: Свободный остаток(В ед. хранения);</t>
@@ -62,21 +62,42 @@
     <t>Картонна коробка "Новорічні іграшки" (26-14*4 )</t>
   </si>
   <si>
-    <t>Коробка "Куб синій з оленем" (26-03*2 )</t>
-  </si>
-  <si>
     <t>МРІЯ</t>
   </si>
   <si>
     <t>ДЕСЕРТИ</t>
   </si>
   <si>
+    <t>Lacmi Гарячий шоколад УБ 20г /90шт</t>
+  </si>
+  <si>
+    <t>Lacmi Гарячий шоколад УБ 20г /90шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Желе ананас УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе ананас УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желе ананас УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе апельсин УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе апельсин УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желе вишня УБ 78г /56шт</t>
+  </si>
+  <si>
+    <t>Желе вишня УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Желе вишня УБ 78г /56шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
     <t>Желе ківі УБ 78г /56шт</t>
   </si>
   <si>
@@ -89,21 +110,24 @@
     <t>Желе ківі УБ 78г /56шт АКЦІЯ ОПТ</t>
   </si>
   <si>
+    <t>Желе Лісова ягода УБ 78г /56шт</t>
+  </si>
+  <si>
     <t>Желе Лісова ягода УБ 78г /56шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Желе полуниця УБ 78г /56шт</t>
   </si>
   <si>
+    <t>Желе полуниця УБ 78г /56шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Какао-порошок 22% УБ 60г /26шт</t>
   </si>
   <si>
     <t>Какао-порошок УБ 80г /48шт</t>
   </si>
   <si>
-    <t>Какао-порошок УБ 80г /48шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>ДОБАВКИ</t>
   </si>
   <si>
@@ -113,6 +137,9 @@
     <t>Ванільний цукор УБ 10г /58шт</t>
   </si>
   <si>
+    <t>Ванільний цукор УБ 35г /36шт</t>
+  </si>
+  <si>
     <t>Глазур для паски біла УБ 75г /40шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -122,39 +149,51 @@
     <t>Желатин УБ 25г /42шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Желатин УБ 25г /42шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 100г /48шт /</t>
   </si>
   <si>
-    <t>Лимонна кислота УБ 100г /48шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Лимонна кислота УБ 100г /48шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Лимонна кислота УБ 25г /55шт</t>
   </si>
   <si>
     <t>Суміш для приготування Грибного соусу УБ 36г /34шт</t>
   </si>
   <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт /</t>
+  </si>
+  <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт /АКЦІЯ</t>
+  </si>
+  <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Суміш для приготування Грибного соусу УБ 36г /34шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт</t>
   </si>
   <si>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт /</t>
+  </si>
+  <si>
+    <t>Суміш для приготування соусу Болоньєзе УБ 40г /32шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Суміш для приготування соусу Карбонара УБ 36г /34шт</t>
   </si>
   <si>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт /</t>
+  </si>
+  <si>
+    <t>Суміш для приготування соусу Карбонара УБ 36г /34шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>ПРИПРАВИ</t>
   </si>
   <si>
     <t>Приправа до картоплі УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Приправа до картоплі УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -167,18 +206,12 @@
     <t>Приправа до м'яса УБ 25г /34шт</t>
   </si>
   <si>
-    <t>Приправа до м'яса УБ 25г /34шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Приправа до м'яса УБ 25г /34шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт</t>
   </si>
   <si>
-    <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Приправа до моркви по-корейськи УБ 20г /48шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -191,9 +224,6 @@
     <t>Приправа до риби УБ 25г /30шт</t>
   </si>
   <si>
-    <t>Приправа до риби УБ 25г /30шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Приправа до риби УБ 25г /30шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -215,15 +245,9 @@
     <t>Суміш овочів та спецій УБ 20г /32шт</t>
   </si>
   <si>
-    <t>Суміш овочів та спецій УБ 20г /32шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт</t>
   </si>
   <si>
-    <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Суміш прянощів «Хмелі-сунелі» по-грузинськи УБ 20г /24шт АКЦІЯ ВІП</t>
   </si>
   <si>
@@ -239,18 +263,12 @@
     <t>Томати з часником та базиліком УБ 20г /30шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Часник гранульований сушений УБ 15г /42шт</t>
-  </si>
-  <si>
     <t>Часник гранульований сушений УБ 15г /42шт /</t>
   </si>
   <si>
     <t>Часник гранульований сушений УБ 15г /42шт /АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Часник гранульований сушений УБ 15г /42шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>СПЕЦІЇ</t>
   </si>
   <si>
@@ -263,9 +281,6 @@
     <t>Коріандр мелений УБ 20г /30шт</t>
   </si>
   <si>
-    <t>Коріандр мелений УБ 20г /30шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Куркума мелена УБ 15г /38шт</t>
   </si>
   <si>
@@ -281,9 +296,6 @@
     <t>Перець духмяний УБ 15г /30шт</t>
   </si>
   <si>
-    <t>Перець духмяний УБ 20г /22шт</t>
-  </si>
-  <si>
     <t>Перець червоний мелений УБ 20г /32шт</t>
   </si>
   <si>
@@ -296,7 +308,7 @@
     <t>Перець чорний мелений УБ 20г /38шт</t>
   </si>
   <si>
-    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ</t>
+    <t>Перець чорний мелений УБ 20г /38шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Суміш перців з прянощами подрібнена УБ 30г /24шт</t>
@@ -317,18 +329,15 @@
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ Цінова</t>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN "Double peanuts" мол-шок з арахісом та арахісовим кремом ВКФ 39г /180шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /</t>
   </si>
   <si>
@@ -338,39 +347,24 @@
     <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN з начинкою ВКФ 43г /180шт /АКЦІЯ Цінова накладна</t>
-  </si>
-  <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з карамельною начинкою ВКФ 40г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ Цінова</t>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Батон ROSHEN мол-шок з кокосом та мигдалем ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP</t>
   </si>
   <si>
@@ -380,15 +374,9 @@
     <t>Батон ROSHEN молочно-шоколадний з арахісовою начинкою ВКФ 38г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт /АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP</t>
   </si>
   <si>
-    <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Батон ROSHEN молочно-шоколадний з начинкою крем-брюле ВКФ 43г /180шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -404,15 +392,9 @@
     <t>Бісквіт Рошен П'янка вишня ВКФ 300г /9шт</t>
   </si>
   <si>
-    <t>Бісквіт Рошен Празький ВКФ 300г /9шт</t>
-  </si>
-  <si>
     <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт</t>
   </si>
   <si>
-    <t>РУЛЕТ Золотий ключик ВКФ 180г /14шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>РУЛЕТ П'янка вишня ВКФ 180г /14шт</t>
   </si>
   <si>
@@ -422,21 +404,12 @@
     <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Choco Fest ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Milk Party ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт</t>
   </si>
   <si>
-    <t>Тістечка Too Cool Strawberry Splash ВКФ 270г /12шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>ВАФЛІ ФАСОВАНІ</t>
   </si>
   <si>
@@ -446,16 +419,16 @@
     <t>Konafetto з ванільною начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>KONAFETTO з ванільною начинкою ВКФ 140г /15шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
-    <t>KONAFETTO з горіховою начинкою ВКФ 140г /15шт АКЦІЯ</t>
+    <t>Konafetto з горіховою начинкою ВКФ 140г /15шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Konafetto з кокосовою начинкою ВКФ 140г /15шт</t>
   </si>
   <si>
-    <t>KONAFETTO з молочною начинкою ВКФ 140г /15шт АКЦІЯ ВІП 1</t>
+    <t>Konafetto з молочною начинкою ВКФ 140г /15шт</t>
+  </si>
+  <si>
+    <t>KONAFETTO з молочною начинкою ВКФ 140г /15шт DE</t>
   </si>
   <si>
     <t>Roshetto dark ВКФ 34г /200шт</t>
@@ -467,63 +440,42 @@
     <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Roshetto milk ВКФ 34г /200шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Roshetto Peanut ВКФ 34г /200шт</t>
   </si>
   <si>
-    <t>Roshetto Peanut ВКФ 34г /200шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт /АКЦІЯ ВІП</t>
+    <t>Wafers Sandwich Crunch ваніль ККФ 142г /15шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch горіх ККФ 142г /15шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch какао ККФ 142г /15шт /АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт /АКЦІЯ ВІП</t>
+    <t>Wafers Sandwich Crunch лимон ККФ 142г /15шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт /</t>
   </si>
   <si>
-    <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт /АКЦІЯ ВІП</t>
+    <t>Wafers Sandwich Crunch полуниця ККФ 142г /15шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Wafers горіх ВКФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers горіх ВКФ 216г /16шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Wafers горіх ВКФ 72г /22шт AR /</t>
   </si>
   <si>
     <t>Wafers горіх ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers горіх ККФ 216г /16шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Wafers какао ККФ 216г /16шт</t>
   </si>
   <si>
@@ -542,18 +494,12 @@
     <t>Wafers лимон ККФ 216г /16шт</t>
   </si>
   <si>
-    <t>Wafers лимон ККФ 216г /16шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /</t>
   </si>
   <si>
     <t>Wafers молоко ВКФ 72г /22шт AR /АКЦІЯ</t>
   </si>
   <si>
-    <t>Wafers молоко ВКФ 72г /22шт AR /АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Wafers молоко ККФ 216г /16шт</t>
   </si>
   <si>
@@ -599,16 +545,7 @@
     <t>Yummi Gummi Banana Land ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Banana Land ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Carrot Farm ВКФ 70г /22шт АКЦІЯ Цінова</t>
+    <t>Yummi Gummi Cactus ВКФ 165г /14шт</t>
   </si>
   <si>
     <t>Yummi Gummi Carrots ВКФ 70г /22шт</t>
@@ -617,78 +554,36 @@
     <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Cheesecakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Cherry ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Cherry ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi CupCakes ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi CupCakes ВКФ 70г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Daydream ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Donuts ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Donuts ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Duo Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fizzy Worms ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт</t>
   </si>
   <si>
+    <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Yummi Gummi Fluffi Barbecue ВКФ 200г /7шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
@@ -698,19 +593,19 @@
     <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Rainbow Turbines ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffi Soft Hearts ВКФ 65г /11шт АКЦІЯ Цінова накладна UA</t>
@@ -719,52 +614,31 @@
     <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова UA</t>
+    <t>Yummi Gummi Fluffi Teeny Tiny Bits ВКФ 65г /11шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Fluffy Sheep ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Frozen Yogo ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Funny Cola ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Galaxy Life ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ ВІП</t>
+    <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт</t>
   </si>
   <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 165г /14шт АКЦІЯ Цінова</t>
@@ -773,78 +647,63 @@
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Mini Bear Mix ВКФ 70г /22шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
-    <t>Yummi Gummi Pasta ВКФ 70г /22шт АКЦІЯ</t>
+    <t>Yummi Gummi Pasta ВКФ 70г /22шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Rabbits ВКФ 165г /14шт</t>
+  </si>
+  <si>
+    <t>Yummi Gummi Rainbow Wands ВКФ 165г /14шт</t>
   </si>
   <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Smile Mix ВКФ 70г /22шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Belts ВКФ 70г /40шт АКЦІЯ Цінова накладна</t>
   </si>
   <si>
+    <t>Yummi Gummi Sour Slices ВКФ 165г /14шт</t>
+  </si>
+  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Sticks ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ RO</t>
   </si>
   <si>
-    <t>Yummi Gummi Sour Strawberries ВКФ 70г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Yummi Gummi Twists ВКФ 70г /40шт АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт</t>
   </si>
   <si>
-    <t>Yummi Gummi Watermelon Slices ВКФ 70г /22шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Бім-Бом РЦ 200г /11шт</t>
   </si>
   <si>
     <t>Джеллі РЦ 200г /13шт</t>
   </si>
   <si>
+    <t>Джеллі РЦ 200г /13шт АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Льодяник мікс РЦ 200г /24шт /</t>
   </si>
   <si>
@@ -899,9 +758,6 @@
     <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт</t>
   </si>
   <si>
-    <t>LolliPops з йогуртовими смаками РЦ 0.92кг /9шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>LolliPops з коктельними смаками РЦ 0.92кг /9шт /</t>
   </si>
   <si>
@@ -983,57 +839,54 @@
     <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ ВІП 1</t>
+    <t>Assortment Classic ВКФ 154г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Assortment Elegant 145г/8</t>
   </si>
   <si>
-    <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
-    <t>Cherry Queen heart РЦ 122г /8шт АКЦІЯ ВІП</t>
+    <t>Assortment Elegant ВКФ 145г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Chocolateria ВКФ 194г /8шт NEW</t>
   </si>
   <si>
-    <t>Chocolateria ВКФ 194г /8шт NEW АКЦІЯ</t>
-  </si>
-  <si>
     <t>Chocolateria ВКФ 256г /8шт</t>
   </si>
   <si>
     <t>Roshen Compliment ВКФ 145г /8шт</t>
   </si>
   <si>
-    <t>Roshen Compliment ВКФ 145г /8шт АКЦІЯ ВІП 1</t>
+    <t>Roshen Compliment ВКФ 145г /8шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /</t>
   </si>
   <si>
-    <t>Roshen вишня з вишневим лікером ВКФ 155г /10шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Shooters віски-лікер ВКФ 150г /10шт /</t>
   </si>
   <si>
+    <t>Shooters віски-лікер ВКФ 150г /10шт /АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Shooters з бренді-лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
+    <t>Shooters з бренді-лікером ВКФ 150г /10шт /АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Shooters з ромовим лікером ВКФ 150г /10шт /</t>
   </si>
   <si>
+    <t>Shooters з ромовим лікером ВКФ 150г /10шт /АКЦІЯ ВІП 1</t>
+  </si>
+  <si>
     <t>Київ вечірній ВКФ 176г /7шт</t>
   </si>
   <si>
     <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ</t>
   </si>
   <si>
-    <t>Київ вечірній ВКФ 176г /7шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Київ вечірній ВКФ 352г /7шт</t>
   </si>
   <si>
@@ -1049,7 +902,10 @@
     <t>2 CRACK з молочно-ванільною начинкою ККФ 190г /26шт</t>
   </si>
   <si>
-    <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт АКЦІЯ ВІП 1</t>
+    <t>2 CRACK з начинкою какао-горіх ККФ 190г /26шт</t>
+  </si>
+  <si>
+    <t>2 CRACK з шоколадною начинкою ККФ 190г /26шт</t>
   </si>
   <si>
     <t>2 CRACK з шоколадною начинкою ККФ 190г /28шт</t>
@@ -1058,18 +914,9 @@
     <t>Butter Cookies з маслом класичне ВКФ 140г /12шт</t>
   </si>
   <si>
-    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Butter Cookies з маслом класичне ВКФ 140г /12шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Butter Cookies з маслом та какао ВКФ 140г /12шт</t>
   </si>
   <si>
-    <t>Butter Cookies з маслом та какао ВКФ 140г /12шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Lovita Blondie Brownie з кокосом ККФ 152г /21шт</t>
   </si>
   <si>
@@ -1085,9 +932,6 @@
     <t>Lovita Cake Cookies з полуничною начинкою ККФ 168г /16шт</t>
   </si>
   <si>
-    <t>Lovita Cake Cookies з полуничною начинкою ККФ 168г /16шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Lovita Cake Cookies з яблуком та корицею ККФ 168г /16шт</t>
   </si>
   <si>
@@ -1100,16 +944,13 @@
     <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт</t>
   </si>
   <si>
-    <t>Lovita Classic Cookies з кусочками глазурі ВКФ 150г /16шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 135г /21шт /</t>
   </si>
   <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком апельсину ККФ 420г /7шт</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 135г /21шт /АКЦІЯ ВІП 1</t>
+    <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 135г /21шт /</t>
   </si>
   <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком малини ККФ 420г /7шт</t>
@@ -1118,9 +959,6 @@
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /</t>
   </si>
   <si>
-    <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 135г /21шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lovita Jelly Cookies з желейною начинкою зі смаком полуниці ККФ 420г /7шт</t>
   </si>
   <si>
@@ -1133,49 +971,37 @@
     <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Lovita Soft Cream Cookies cocoa ККФ 127г /18шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Lovita Soft Cream Cookies hazelnut ККФ 127г /18шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт</t>
   </si>
   <si>
-    <t>Lovita Soft Cream Cookies milk ККФ 127г /18шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Lovita Soft Cream Cookies Peanut ККФ 127г /18шт</t>
   </si>
   <si>
     <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з молочно-кремовою начинкою ККФ 180г /28шт FP АКЦІЯ</t>
-  </si>
-  <si>
     <t>Multicake з начинкою какао ККФ 180г /28шт FP</t>
   </si>
   <si>
     <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP АКЦІЯ</t>
+    <t>Multicake з начинкою кокос-крем ККФ 180г /28шт FP DE</t>
   </si>
   <si>
     <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
+    <t>Multicake з начинкою лимон-крем ККФ 180г /28шт FP DE</t>
+  </si>
+  <si>
     <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP</t>
   </si>
   <si>
-    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт FP АКЦІЯ</t>
+    <t>Multicake з начинкою полуниця-крем ККФ 180г /28шт АКЦІЯ</t>
   </si>
   <si>
     <t>До кави масло-ваніль ВКФ 185г /28шт /</t>
@@ -1193,31 +1019,13 @@
     <t>До кави пряжене молоко ККФ 370г /24шт</t>
   </si>
   <si>
-    <t>КРЕКЕР 2 CRACK з молочно-ванільною начинкою ККФ 235г /14шт</t>
-  </si>
-  <si>
-    <t>ПОДАРУНКИ</t>
-  </si>
-  <si>
-    <t>ПОДАРУНКИ 2026</t>
-  </si>
-  <si>
-    <t>Н/п №3 26 Автомобіль Санти РЦ 330г /9шт</t>
-  </si>
-  <si>
-    <t>Н/п №7 26 Різдвяне небо РЦ 509г /6шт</t>
-  </si>
-  <si>
-    <t>Набір кондитерських виробів4</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ВАГОВІ</t>
   </si>
   <si>
     <t>Boo! Bear РЦ 1кг /5пак</t>
   </si>
   <si>
-    <t>Boo! Bear РЦ 1кг /5пак ЗНИЖКА ДИСТР</t>
+    <t>Boo! Bear РЦ 1кг /5пак АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT</t>
@@ -1226,7 +1034,7 @@
     <t>Candy Nut м'яка карамель з арахісом ВКФ 1кг /8пак PT АКЦІЯ ВІП 1</t>
   </si>
   <si>
-    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак ЗНИЖКА ДИСТР</t>
+    <t>Candy Nut нуга і м'яка карамель з арахісом ВКФ 1кг /5пак АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Candy Nut нуга карамель арахіс 1кг/5</t>
@@ -1235,6 +1043,9 @@
     <t>Flaksi какао ККФ 0.5кг /8пак</t>
   </si>
   <si>
+    <t>Flaksi кокос ККФ 0.5кг /8пак</t>
+  </si>
+  <si>
     <t>Galaretka Roshen РЦ 1кг /9пак</t>
   </si>
   <si>
@@ -1244,9 +1055,6 @@
     <t>Johnny Krocker choco ВКФ 1кг /4шт PL</t>
   </si>
   <si>
-    <t>Johnny Krocker choco ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Johnny Krocker coconut ВКФ 1кг /4шт</t>
   </si>
   <si>
@@ -1259,16 +1067,10 @@
     <t>Johnny Krocker milk ВКФ 1кг /4шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
-    <t>Ko-Ko Choco White 1кг/5</t>
-  </si>
-  <si>
-    <t>Ko-Ko Choco White ВКФ 1кг /5пак АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>KONAFETTO blanc ККФ 1кг /5пак /</t>
-  </si>
-  <si>
-    <t>KONAFETTO nero ККФ 1кг /5пак /</t>
+    <t>KONAFETTO blanc ККФ 1кг /5пак HAL</t>
+  </si>
+  <si>
+    <t>KONAFETTO nero ККФ 1кг /5пак HAL</t>
   </si>
   <si>
     <t>Krock з арахісовою пастою ВКФ 1кг /8пак</t>
@@ -1289,12 +1091,12 @@
     <t>Кара-Кум ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
   </si>
   <si>
+    <t>Кара-Кум ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ліщина 1кг/6 ВКФ</t>
   </si>
   <si>
-    <t>Ліщина ВКФ 1кг /6пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>Монблан з карамелізованим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
@@ -1304,21 +1106,36 @@
     <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з подрібненим мигдалем ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з цільним лісовим горіхом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан з шоколадом та сезамом ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак</t>
   </si>
   <si>
+    <t>Монблан крем-праліне+подрібнений лісовий горіх ВКФ 1кг /4пак ЗНИЖКА ДИСТР</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак</t>
   </si>
   <si>
     <t>Ромашка ВКФ 1кг /9пак АКЦІЯ</t>
   </si>
   <si>
+    <t>Ромашка ВКФ 1кг /9пак АКЦІЯ ВІП</t>
+  </si>
+  <si>
     <t>Ромашка ВКФ 1кг /9пак ЗНИЖКА ДИСТР</t>
   </si>
   <si>
@@ -1331,15 +1148,9 @@
     <t>Червоний мак ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
   </si>
   <si>
-    <t>Червоний мак ВКФ 1кг /7пак ЗНИЖКА ДИСТР</t>
-  </si>
-  <si>
     <t>Шоколапки ВКФ 1кг /7пак</t>
   </si>
   <si>
-    <t>Шоколапки ВКФ 1кг /7пак АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
     <t>ЦУКЕРКИ ШОКОЛАДНІ ФАСОВАНІ</t>
   </si>
   <si>
@@ -1349,18 +1160,15 @@
     <t>Johnny Krocker coconut ВКФ 350г /12шт</t>
   </si>
   <si>
+    <t>Johnny Krocker milk ВКФ 350г /12шт PL</t>
+  </si>
+  <si>
     <t>Монблан РЦ 240г /15шт /</t>
   </si>
   <si>
     <t>ШОКОЛАД</t>
   </si>
   <si>
-    <t>Lacmi Big Bite молочний ВКФ 200г /17шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Lacmi Big Bite молочний ВКФ 260г /15шт /</t>
-  </si>
-  <si>
     <t>Lacmi Big Bite молочний ВКФ 260г /15шт /АКЦІЯ ВІП 1</t>
   </si>
   <si>
@@ -1376,42 +1184,21 @@
     <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi Black, White &amp; Caramel молочний з молочною начинкою, карамеллю та печивом з какао ВКФ 100г /18шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт UA TP</t>
-  </si>
-  <si>
-    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт АКЦІЯ ОПТ</t>
+    <t>Lacmi Cool-Nut-Coconut молочний з мигдалем та кокосом ВКФ 280г /12шт</t>
   </si>
   <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт</t>
   </si>
   <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi Crumble-Bumble ВКФ 83г /22шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт</t>
   </si>
   <si>
     <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi Fun&amp;Crispy молочний пористий з молочною начинкою з кріспі ВКФ 85г /17шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний Strawberry cake ВКФ 275г /12шт</t>
   </si>
   <si>
@@ -1421,22 +1208,19 @@
     <t>Lacmi молочний ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ВІП</t>
+    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з арахісом і карамельно-арахісовою начинкою ВКФ 295г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт</t>
@@ -1445,73 +1229,40 @@
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт UA TP АКЦІЯ ВІП</t>
+    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ВІП</t>
   </si>
   <si>
     <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з арахісом, карамельною та арахісовою начинками ВКФ 87г /22шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
     <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з мигдалем та кокосовим кремом ВКФ 84г /22шт АКЦІЯ Цінова UA</t>
+    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ВІП</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт UA TP АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з молочною начинкою та печивом ВКФ 100г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт UA TP</t>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з молочною та шоколадною начинками, вафлею з какао ВКФ 235г /12шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ Цінова UA</t>
+    <t>Lacmi молочний з начинкою зі смаком "Полунична панакота" ВКФ 90г /22шт АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт</t>
@@ -1523,9 +1274,6 @@
     <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Lacmi молочний з начинкою зі смаком "Тірамісу" та печивом ВКФ 270г /12шт АКЦІЯ</t>
-  </si>
-  <si>
     <t>Lacmi молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
@@ -1544,58 +1292,43 @@
     <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ Цінова</t>
+    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ ВІП</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з шоколадно-горіховою начинкою та печивом ВКФ 265г /12шт АКЦІЯ ОПТ</t>
+  </si>
+  <si>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт</t>
   </si>
   <si>
     <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP</t>
   </si>
   <si>
-    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт АКЦІЯ ОПТ</t>
+    <t>Lacmi молочний з шоколадною начинкою та вафлею ВКФ 90г /18шт UA TP АКЦІЯ ОПТ</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen Nut молочний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
   </si>
   <si>
     <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
+    <t>Roshen Nut молочний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
+  </si>
+  <si>
     <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>Roshen Nut чорний з цілим мигдалем ВКФ 90г /20шт АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
     <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт</t>
   </si>
   <si>
-    <t>Roshen Nut чорний з цілим фундуком ВКФ 90г /18шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
     <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт FP АКЦІЯ Цінова UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
-    <t>Roshen пористий білий карамельний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
+    <t>Roshen пористий БІЛИЙ ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
     <t>Roshen пористий екстрачорний ВКФ 80г /20шт Aerated UA</t>
@@ -1610,27 +1343,21 @@
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA</t>
   </si>
   <si>
-    <t>Roshen пористий молочний ВКФ 80г /20шт Aerated UA АКЦІЯ ОПТ</t>
-  </si>
-  <si>
     <t>Roshen пористий молочний ВКФ 80г /20шт Aerated АКЦІЯ Цінова</t>
   </si>
   <si>
+    <t>Roshen пористий молочний ВКФ 80г /20шт UA</t>
+  </si>
+  <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт</t>
   </si>
   <si>
     <t>Roshen чорний Bitter 80% ВКФ 85г /35шт АКЦІЯ ОПТ</t>
   </si>
   <si>
-    <t>Roshen Чорний Brut 80% ВКФ 85г /35шт /АКЦИЯ ВИП</t>
-  </si>
-  <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /</t>
   </si>
   <si>
-    <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ</t>
-  </si>
-  <si>
     <t>Roshen чорний Special 56% ВКФ 85г /35шт /АКЦІЯ ОПТ</t>
   </si>
   <si>
@@ -1643,37 +1370,10 @@
     <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт</t>
   </si>
   <si>
-    <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт АКЦІЯ ВІП</t>
+    <t>TIDBIT з начинкою зі смаком "Вишневий Брауні" ВКФ 50г /28шт АКЦІЯ ВІП 1</t>
   </si>
   <si>
     <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт</t>
-  </si>
-  <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ ВІП 1</t>
-  </si>
-  <si>
-    <t>TIDBIT з нугою і м'якою карамеллю з арахісом ВКФ 50г /24шт АКЦІЯ Цінова</t>
-  </si>
-  <si>
-    <t>ФІГУРКИ</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 25г /35шт</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 25г /35шт АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO</t>
-  </si>
-  <si>
-    <t>Святий Миколай Roshen ВКФ 40г /24шт UA, BG, RO АКЦІЯ ВІП</t>
-  </si>
-  <si>
-    <t>Сніговик Roshen ВКФ 45г /20шт UA, BG, RO</t>
   </si>
 </sst>
 </file>
@@ -1847,7 +1547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -1903,12 +1603,6 @@
     <xf numFmtId="52" fontId="5" fillId="5" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="3" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf fontId="5" fillId="4" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1928,7 +1622,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false"/>
   </sheetPr>
-  <dimension ref="C552"/>
+  <dimension ref="C452"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="true"/>
@@ -1993,7 +1687,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>903</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12" ht="11" customHeight="true">
@@ -2001,7 +1695,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>939275</v>
+        <v>977289</v>
       </c>
     </row>
     <row r="13" ht="11" customHeight="true" outlineLevel="1">
@@ -2009,7 +1703,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="14" t="n">
-        <v>116</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" ht="11" customHeight="true" outlineLevel="2">
@@ -2020,52 +1714,52 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B15" s="15" t="s">
+    <row r="15" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B15" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="11" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B16" s="13" t="s">
+      <c r="C15" s="12" t="n">
+        <v>267889</v>
+      </c>
+    </row>
+    <row r="16" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B16" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>217931</v>
-      </c>
-    </row>
-    <row r="17" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B17" s="16" t="s">
+        <v>21453</v>
+      </c>
+    </row>
+    <row r="17" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B17" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="12" t="n">
-        <v>20263</v>
+      <c r="C17" s="18" t="n">
+        <v>1727</v>
       </c>
     </row>
     <row r="18" ht="11" customHeight="true" outlineLevel="3">
       <c r="B18" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="18" t="n">
-        <v>2845</v>
+      <c r="C18" s="11" t="n">
+        <v>907</v>
       </c>
     </row>
     <row r="19" ht="11" customHeight="true" outlineLevel="3">
       <c r="B19" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>178</v>
+      <c r="C19" s="18" t="n">
+        <v>2681</v>
       </c>
     </row>
     <row r="20" ht="11" customHeight="true" outlineLevel="3">
       <c r="B20" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="18" t="n">
-        <v>4200</v>
+      <c r="C20" s="11" t="n">
+        <v>724</v>
       </c>
     </row>
     <row r="21" ht="11" customHeight="true" outlineLevel="3">
@@ -2073,7 +1767,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" ht="11" customHeight="true" outlineLevel="3">
@@ -2081,15 +1775,15 @@
         <v>21</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>555</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" ht="11" customHeight="true" outlineLevel="3">
       <c r="B23" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="11" t="n">
-        <v>824</v>
+      <c r="C23" s="18" t="n">
+        <v>1484</v>
       </c>
     </row>
     <row r="24" ht="11" customHeight="true" outlineLevel="3">
@@ -2097,23 +1791,23 @@
         <v>23</v>
       </c>
       <c r="C24" s="18" t="n">
-        <v>1412</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="25" ht="11" customHeight="true" outlineLevel="3">
       <c r="B25" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="18" t="n">
-        <v>3549</v>
+      <c r="C25" s="11" t="n">
+        <v>896</v>
       </c>
     </row>
     <row r="26" ht="11" customHeight="true" outlineLevel="3">
       <c r="B26" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="18" t="n">
-        <v>1055</v>
+      <c r="C26" s="11" t="n">
+        <v>89</v>
       </c>
     </row>
     <row r="27" ht="11" customHeight="true" outlineLevel="3">
@@ -2121,7 +1815,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="18" t="n">
-        <v>5293</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="28" ht="11" customHeight="true" outlineLevel="3">
@@ -2129,31 +1823,31 @@
         <v>27</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="29" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B29" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B29" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="12" t="n">
-        <v>89573</v>
+      <c r="C29" s="18" t="n">
+        <v>1008</v>
       </c>
     </row>
     <row r="30" ht="11" customHeight="true" outlineLevel="3">
       <c r="B30" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="18" t="n">
-        <v>6029</v>
+      <c r="C30" s="11" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="31" ht="11" customHeight="true" outlineLevel="3">
       <c r="B31" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="18" t="n">
-        <v>28214</v>
+      <c r="C31" s="11" t="n">
+        <v>155</v>
       </c>
     </row>
     <row r="32" ht="11" customHeight="true" outlineLevel="3">
@@ -2161,23 +1855,23 @@
         <v>31</v>
       </c>
       <c r="C32" s="18" t="n">
-        <v>4794</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="33" ht="11" customHeight="true" outlineLevel="3">
       <c r="B33" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="18" t="n">
-        <v>22598</v>
+      <c r="C33" s="11" t="n">
+        <v>292</v>
       </c>
     </row>
     <row r="34" ht="11" customHeight="true" outlineLevel="3">
       <c r="B34" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="11" t="n">
-        <v>722</v>
+      <c r="C34" s="18" t="n">
+        <v>1260</v>
       </c>
     </row>
     <row r="35" ht="11" customHeight="true" outlineLevel="3">
@@ -2185,7 +1879,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="18" t="n">
-        <v>12925</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="36" ht="11" customHeight="true" outlineLevel="3">
@@ -2193,23 +1887,23 @@
         <v>35</v>
       </c>
       <c r="C36" s="18" t="n">
-        <v>3252</v>
-      </c>
-    </row>
-    <row r="37" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B37" s="17" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="37" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B37" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="18" t="n">
-        <v>6870</v>
+      <c r="C37" s="12" t="n">
+        <v>145597</v>
       </c>
     </row>
     <row r="38" ht="11" customHeight="true" outlineLevel="3">
       <c r="B38" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C38" s="11" t="n">
-        <v>43</v>
+      <c r="C38" s="18" t="n">
+        <v>4339</v>
       </c>
     </row>
     <row r="39" ht="11" customHeight="true" outlineLevel="3">
@@ -2217,39 +1911,39 @@
         <v>38</v>
       </c>
       <c r="C39" s="18" t="n">
-        <v>1492</v>
+        <v>96921</v>
       </c>
     </row>
     <row r="40" ht="11" customHeight="true" outlineLevel="3">
       <c r="B40" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="11" t="n">
-        <v>906</v>
+      <c r="C40" s="18" t="n">
+        <v>2213</v>
       </c>
     </row>
     <row r="41" ht="11" customHeight="true" outlineLevel="3">
       <c r="B41" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="11" t="n">
-        <v>842</v>
+      <c r="C41" s="18" t="n">
+        <v>4794</v>
       </c>
     </row>
     <row r="42" ht="11" customHeight="true" outlineLevel="3">
       <c r="B42" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="11" t="n">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="43" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B43" s="16" t="s">
+      <c r="C42" s="18" t="n">
+        <v>22427</v>
+      </c>
+    </row>
+    <row r="43" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B43" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="12" t="n">
-        <v>32062</v>
+      <c r="C43" s="11" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="44" ht="11" customHeight="true" outlineLevel="3">
@@ -2257,15 +1951,15 @@
         <v>43</v>
       </c>
       <c r="C44" s="18" t="n">
-        <v>1146</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="true" outlineLevel="3">
       <c r="B45" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="11" t="n">
-        <v>1</v>
+      <c r="C45" s="18" t="n">
+        <v>5349</v>
       </c>
     </row>
     <row r="46" ht="11" customHeight="true" outlineLevel="3">
@@ -2273,7 +1967,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>698</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" ht="11" customHeight="true" outlineLevel="3">
@@ -2281,23 +1975,23 @@
         <v>46</v>
       </c>
       <c r="C47" s="18" t="n">
-        <v>2291</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="48" ht="11" customHeight="true" outlineLevel="3">
       <c r="B48" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="18" t="n">
-        <v>1229</v>
-      </c>
-    </row>
-    <row r="49" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C48" s="11" t="n">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="true" outlineLevel="3">
       <c r="B49" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C49" s="18" t="n">
-        <v>2751</v>
+      <c r="C49" s="11" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="50" ht="11" customHeight="true" outlineLevel="3">
@@ -2305,7 +1999,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" ht="11" customHeight="true" outlineLevel="3">
@@ -2313,7 +2007,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>964</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52" ht="11" customHeight="true" outlineLevel="3">
@@ -2321,15 +2015,15 @@
         <v>51</v>
       </c>
       <c r="C52" s="18" t="n">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="53" ht="11" customHeight="true" outlineLevel="3">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="true" outlineLevel="3">
       <c r="B53" s="17" t="s">
         <v>52</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" ht="11" customHeight="true" outlineLevel="3">
@@ -2337,7 +2031,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>743</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" ht="11" customHeight="true" outlineLevel="3">
@@ -2345,23 +2039,23 @@
         <v>54</v>
       </c>
       <c r="C55" s="18" t="n">
-        <v>1966</v>
-      </c>
-    </row>
-    <row r="56" ht="11" customHeight="true" outlineLevel="3">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="true" outlineLevel="3">
       <c r="B56" s="17" t="s">
         <v>55</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B57" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B57" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="18" t="n">
-        <v>2277</v>
+      <c r="C57" s="12" t="n">
+        <v>43065</v>
       </c>
     </row>
     <row r="58" ht="11" customHeight="true" outlineLevel="3">
@@ -2369,7 +2063,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>1</v>
+        <v>886</v>
       </c>
     </row>
     <row r="59" ht="11" customHeight="true" outlineLevel="3">
@@ -2377,7 +2071,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>630</v>
+        <v>655</v>
       </c>
     </row>
     <row r="60" ht="11" customHeight="true" outlineLevel="3">
@@ -2385,7 +2079,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="18" t="n">
-        <v>1013</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="61" ht="11" customHeight="true" outlineLevel="3">
@@ -2393,7 +2087,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>898</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" ht="11" customHeight="true" outlineLevel="3">
@@ -2401,7 +2095,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="18" t="n">
-        <v>1402</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="63" ht="11" customHeight="true" outlineLevel="3">
@@ -2409,7 +2103,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>437</v>
+        <v>502</v>
       </c>
     </row>
     <row r="64" ht="11" customHeight="true" outlineLevel="3">
@@ -2417,7 +2111,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="18" t="n">
-        <v>1380</v>
+        <v>3394</v>
       </c>
     </row>
     <row r="65" ht="11" customHeight="true" outlineLevel="3">
@@ -2425,47 +2119,47 @@
         <v>64</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>413</v>
+        <v>554</v>
       </c>
     </row>
     <row r="66" ht="11" customHeight="true" outlineLevel="3">
       <c r="B66" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C66" s="11" t="n">
-        <v>414</v>
+      <c r="C66" s="18" t="n">
+        <v>2452</v>
       </c>
     </row>
     <row r="67" ht="11" customHeight="true" outlineLevel="3">
       <c r="B67" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="18" t="n">
-        <v>1449</v>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C67" s="11" t="n">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="68" ht="11" customHeight="true" outlineLevel="3">
       <c r="B68" s="17" t="s">
         <v>67</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="true" outlineLevel="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="69" ht="11" customHeight="true" outlineLevel="3">
       <c r="B69" s="17" t="s">
         <v>68</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>858</v>
+        <v>560</v>
       </c>
     </row>
     <row r="70" ht="11" customHeight="true" outlineLevel="3">
       <c r="B70" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="C70" s="11" t="n">
-        <v>942</v>
+      <c r="C70" s="18" t="n">
+        <v>3877</v>
       </c>
     </row>
     <row r="71" ht="11" customHeight="true" outlineLevel="3">
@@ -2473,7 +2167,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>296</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" ht="11" customHeight="true" outlineLevel="3">
@@ -2481,7 +2175,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="18" t="n">
-        <v>1076</v>
+        <v>4861</v>
       </c>
     </row>
     <row r="73" ht="11" customHeight="true" outlineLevel="3">
@@ -2489,15 +2183,15 @@
         <v>72</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>518</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" ht="11" customHeight="true" outlineLevel="3">
       <c r="B74" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="11" t="n">
-        <v>21</v>
+      <c r="C74" s="18" t="n">
+        <v>1735</v>
       </c>
     </row>
     <row r="75" ht="11" customHeight="true" outlineLevel="3">
@@ -2505,39 +2199,39 @@
         <v>74</v>
       </c>
       <c r="C75" s="18" t="n">
-        <v>3996</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="76" ht="11" customHeight="true" outlineLevel="3">
       <c r="B76" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="C76" s="11" t="n">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="77" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C76" s="18" t="n">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="true" outlineLevel="3">
       <c r="B77" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B78" s="16" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="78" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B78" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C78" s="12" t="n">
-        <v>76033</v>
+      <c r="C78" s="18" t="n">
+        <v>2704</v>
       </c>
     </row>
     <row r="79" ht="11" customHeight="true" outlineLevel="3">
       <c r="B79" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C79" s="18" t="n">
-        <v>1793</v>
+      <c r="C79" s="11" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="80" ht="11" customHeight="true" outlineLevel="3">
@@ -2545,39 +2239,39 @@
         <v>79</v>
       </c>
       <c r="C80" s="18" t="n">
-        <v>4052</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="81" ht="11" customHeight="true" outlineLevel="3">
       <c r="B81" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C81" s="18" t="n">
-        <v>2233</v>
+      <c r="C81" s="11" t="n">
+        <v>347</v>
       </c>
     </row>
     <row r="82" ht="11" customHeight="true" outlineLevel="3">
       <c r="B82" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="C82" s="11" t="n">
-        <v>10</v>
+      <c r="C82" s="18" t="n">
+        <v>5587</v>
       </c>
     </row>
     <row r="83" ht="11" customHeight="true" outlineLevel="3">
       <c r="B83" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C83" s="18" t="n">
-        <v>3053</v>
-      </c>
-    </row>
-    <row r="84" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B84" s="17" t="s">
+      <c r="C83" s="11" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="84" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B84" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="18" t="n">
-        <v>12771</v>
+      <c r="C84" s="12" t="n">
+        <v>57774</v>
       </c>
     </row>
     <row r="85" ht="11" customHeight="true" outlineLevel="3">
@@ -2585,7 +2279,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="18" t="n">
-        <v>2636</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="86" ht="11" customHeight="true" outlineLevel="3">
@@ -2593,7 +2287,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="18" t="n">
-        <v>4322</v>
+        <v>5899</v>
       </c>
     </row>
     <row r="87" ht="11" customHeight="true" outlineLevel="3">
@@ -2601,15 +2295,15 @@
         <v>86</v>
       </c>
       <c r="C87" s="18" t="n">
-        <v>4142</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="88" ht="11" customHeight="true" outlineLevel="3">
       <c r="B88" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>8</v>
+      <c r="C88" s="18" t="n">
+        <v>2332</v>
       </c>
     </row>
     <row r="89" ht="11" customHeight="true" outlineLevel="3">
@@ -2617,7 +2311,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="18" t="n">
-        <v>1454</v>
+        <v>5589</v>
       </c>
     </row>
     <row r="90" ht="11" customHeight="true" outlineLevel="3">
@@ -2625,7 +2319,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="18" t="n">
-        <v>8781</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="91" ht="11" customHeight="true" outlineLevel="3">
@@ -2633,7 +2327,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="18" t="n">
-        <v>2304</v>
+        <v>5846</v>
       </c>
     </row>
     <row r="92" ht="11" customHeight="true" outlineLevel="3">
@@ -2641,7 +2335,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="18" t="n">
-        <v>24627</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="93" ht="11" customHeight="true" outlineLevel="3">
@@ -2649,7 +2343,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="18" t="n">
-        <v>1020</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="94" ht="11" customHeight="true" outlineLevel="3">
@@ -2657,7 +2351,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="18" t="n">
-        <v>1273</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="95" ht="11" customHeight="true" outlineLevel="3">
@@ -2665,63 +2359,63 @@
         <v>94</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>748</v>
+        <v>931</v>
       </c>
     </row>
     <row r="96" ht="11" customHeight="true" outlineLevel="3">
       <c r="B96" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="11" t="n">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="97" ht="11" customHeight="true" outlineLevel="1">
-      <c r="B97" s="13" t="s">
+      <c r="C96" s="18" t="n">
+        <v>19059</v>
+      </c>
+    </row>
+    <row r="97" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B97" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C97" s="12" t="n">
-        <v>721228</v>
-      </c>
-    </row>
-    <row r="98" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B98" s="16" t="s">
+      <c r="C97" s="18" t="n">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="98" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B98" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C98" s="12" t="n">
-        <v>182551</v>
-      </c>
-    </row>
-    <row r="99" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C98" s="18" t="n">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="99" ht="11" customHeight="true" outlineLevel="3">
       <c r="B99" s="17" t="s">
         <v>98</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="100" ht="22" customHeight="true" outlineLevel="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="100" ht="11" customHeight="true" outlineLevel="3">
       <c r="B100" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="18" t="n">
-        <v>4059</v>
-      </c>
-    </row>
-    <row r="101" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B101" s="17" t="s">
+      <c r="C100" s="11" t="n">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="101" ht="11" customHeight="true" outlineLevel="1">
+      <c r="B101" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="18" t="n">
-        <v>10752</v>
-      </c>
-    </row>
-    <row r="102" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B102" s="17" t="s">
+      <c r="C101" s="12" t="n">
+        <v>709349</v>
+      </c>
+    </row>
+    <row r="102" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B102" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C102" s="11" t="n">
-        <v>600</v>
+      <c r="C102" s="12" t="n">
+        <v>112847</v>
       </c>
     </row>
     <row r="103" ht="22" customHeight="true" outlineLevel="3">
@@ -2729,31 +2423,31 @@
         <v>102</v>
       </c>
       <c r="C103" s="18" t="n">
-        <v>4450</v>
-      </c>
-    </row>
-    <row r="104" ht="11" customHeight="true" outlineLevel="3">
+        <v>12669</v>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="true" outlineLevel="3">
       <c r="B104" s="17" t="s">
         <v>103</v>
       </c>
       <c r="C104" s="18" t="n">
-        <v>3204</v>
-      </c>
-    </row>
-    <row r="105" ht="11" customHeight="true" outlineLevel="3">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="true" outlineLevel="3">
       <c r="B105" s="17" t="s">
         <v>104</v>
       </c>
       <c r="C105" s="18" t="n">
-        <v>5430</v>
-      </c>
-    </row>
-    <row r="106" ht="11" customHeight="true" outlineLevel="3">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="true" outlineLevel="3">
       <c r="B106" s="17" t="s">
         <v>105</v>
       </c>
       <c r="C106" s="18" t="n">
-        <v>3900</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="107" ht="11" customHeight="true" outlineLevel="3">
@@ -2761,23 +2455,23 @@
         <v>106</v>
       </c>
       <c r="C107" s="18" t="n">
-        <v>14405</v>
-      </c>
-    </row>
-    <row r="108" ht="22" customHeight="true" outlineLevel="3">
+        <v>10672</v>
+      </c>
+    </row>
+    <row r="108" ht="11" customHeight="true" outlineLevel="3">
       <c r="B108" s="17" t="s">
         <v>107</v>
       </c>
       <c r="C108" s="18" t="n">
-        <v>1686</v>
-      </c>
-    </row>
-    <row r="109" ht="22" customHeight="true" outlineLevel="3">
+        <v>12330</v>
+      </c>
+    </row>
+    <row r="109" ht="11" customHeight="true" outlineLevel="3">
       <c r="B109" s="17" t="s">
         <v>108</v>
       </c>
       <c r="C109" s="18" t="n">
-        <v>2786</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="true" outlineLevel="3">
@@ -2785,7 +2479,7 @@
         <v>109</v>
       </c>
       <c r="C110" s="18" t="n">
-        <v>4740</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="true" outlineLevel="3">
@@ -2793,7 +2487,7 @@
         <v>110</v>
       </c>
       <c r="C111" s="18" t="n">
-        <v>15555</v>
+        <v>6601</v>
       </c>
     </row>
     <row r="112" ht="22" customHeight="true" outlineLevel="3">
@@ -2801,7 +2495,7 @@
         <v>111</v>
       </c>
       <c r="C112" s="18" t="n">
-        <v>6960</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="113" ht="22" customHeight="true" outlineLevel="3">
@@ -2809,7 +2503,7 @@
         <v>112</v>
       </c>
       <c r="C113" s="18" t="n">
-        <v>16103</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="114" ht="22" customHeight="true" outlineLevel="3">
@@ -2817,7 +2511,7 @@
         <v>113</v>
       </c>
       <c r="C114" s="18" t="n">
-        <v>10444</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="115" ht="22" customHeight="true" outlineLevel="3">
@@ -2825,7 +2519,7 @@
         <v>114</v>
       </c>
       <c r="C115" s="11" t="n">
-        <v>270</v>
+        <v>480</v>
       </c>
     </row>
     <row r="116" ht="22" customHeight="true" outlineLevel="3">
@@ -2833,7 +2527,7 @@
         <v>115</v>
       </c>
       <c r="C116" s="18" t="n">
-        <v>3909</v>
+        <v>24359</v>
       </c>
     </row>
     <row r="117" ht="22" customHeight="true" outlineLevel="3">
@@ -2841,7 +2535,7 @@
         <v>116</v>
       </c>
       <c r="C117" s="18" t="n">
-        <v>5829</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="118" ht="22" customHeight="true" outlineLevel="3">
@@ -2849,7 +2543,7 @@
         <v>117</v>
       </c>
       <c r="C118" s="18" t="n">
-        <v>26062</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="119" ht="22" customHeight="true" outlineLevel="3">
@@ -2857,7 +2551,7 @@
         <v>118</v>
       </c>
       <c r="C119" s="18" t="n">
-        <v>1140</v>
+        <v>17284</v>
       </c>
     </row>
     <row r="120" ht="22" customHeight="true" outlineLevel="3">
@@ -2865,47 +2559,47 @@
         <v>119</v>
       </c>
       <c r="C120" s="18" t="n">
-        <v>6306</v>
-      </c>
-    </row>
-    <row r="121" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B121" s="17" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="121" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B121" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="C121" s="18" t="n">
-        <v>10928</v>
-      </c>
-    </row>
-    <row r="122" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C121" s="12" t="n">
+        <v>10876</v>
+      </c>
+    </row>
+    <row r="122" ht="11" customHeight="true" outlineLevel="3">
       <c r="B122" s="17" t="s">
         <v>121</v>
       </c>
       <c r="C122" s="18" t="n">
-        <v>17915</v>
-      </c>
-    </row>
-    <row r="123" ht="22" customHeight="true" outlineLevel="3">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="123" ht="11" customHeight="true" outlineLevel="3">
       <c r="B123" s="17" t="s">
         <v>122</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="124" ht="22" customHeight="true" outlineLevel="3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="124" ht="11" customHeight="true" outlineLevel="3">
       <c r="B124" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C124" s="18" t="n">
-        <v>4660</v>
-      </c>
-    </row>
-    <row r="125" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B125" s="16" t="s">
+      <c r="C124" s="11" t="n">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="125" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B125" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="C125" s="12" t="n">
-        <v>12212</v>
+      <c r="C125" s="18" t="n">
+        <v>2386</v>
       </c>
     </row>
     <row r="126" ht="11" customHeight="true" outlineLevel="3">
@@ -2913,15 +2607,15 @@
         <v>125</v>
       </c>
       <c r="C126" s="18" t="n">
-        <v>1439</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="127" ht="11" customHeight="true" outlineLevel="3">
       <c r="B127" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="C127" s="11" t="n">
-        <v>152</v>
+      <c r="C127" s="18" t="n">
+        <v>1471</v>
       </c>
     </row>
     <row r="128" ht="11" customHeight="true" outlineLevel="3">
@@ -2929,7 +2623,7 @@
         <v>127</v>
       </c>
       <c r="C128" s="18" t="n">
-        <v>1094</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="129" ht="11" customHeight="true" outlineLevel="3">
@@ -2937,23 +2631,23 @@
         <v>128</v>
       </c>
       <c r="C129" s="18" t="n">
-        <v>1278</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="130" ht="11" customHeight="true" outlineLevel="3">
       <c r="B130" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="C130" s="18" t="n">
-        <v>1908</v>
-      </c>
-    </row>
-    <row r="131" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B131" s="17" t="s">
+      <c r="C130" s="11" t="n">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="131" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B131" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="C131" s="11" t="n">
-        <v>112</v>
+      <c r="C131" s="12" t="n">
+        <v>161755</v>
       </c>
     </row>
     <row r="132" ht="11" customHeight="true" outlineLevel="3">
@@ -2961,15 +2655,15 @@
         <v>131</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>963</v>
+        <v>818</v>
       </c>
     </row>
     <row r="133" ht="11" customHeight="true" outlineLevel="3">
       <c r="B133" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="C133" s="18" t="n">
-        <v>1536</v>
+      <c r="C133" s="11" t="n">
+        <v>694</v>
       </c>
     </row>
     <row r="134" ht="11" customHeight="true" outlineLevel="3">
@@ -2977,7 +2671,7 @@
         <v>133</v>
       </c>
       <c r="C134" s="11" t="n">
-        <v>308</v>
+        <v>50</v>
       </c>
     </row>
     <row r="135" ht="11" customHeight="true" outlineLevel="3">
@@ -2985,55 +2679,55 @@
         <v>134</v>
       </c>
       <c r="C135" s="11" t="n">
-        <v>214</v>
+        <v>687</v>
       </c>
     </row>
     <row r="136" ht="11" customHeight="true" outlineLevel="3">
       <c r="B136" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="C136" s="11" t="n">
-        <v>639</v>
+      <c r="C136" s="18" t="n">
+        <v>3049</v>
       </c>
     </row>
     <row r="137" ht="11" customHeight="true" outlineLevel="3">
       <c r="B137" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="C137" s="18" t="n">
-        <v>1058</v>
+      <c r="C137" s="11" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="138" ht="11" customHeight="true" outlineLevel="3">
       <c r="B138" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C138" s="11" t="n">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="139" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C138" s="18" t="n">
+        <v>61323</v>
+      </c>
+    </row>
+    <row r="139" ht="11" customHeight="true" outlineLevel="3">
       <c r="B139" s="17" t="s">
         <v>138</v>
       </c>
       <c r="C139" s="18" t="n">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="140" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B140" s="16" t="s">
+        <v>19457</v>
+      </c>
+    </row>
+    <row r="140" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B140" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C140" s="12" t="n">
-        <v>68838</v>
+      <c r="C140" s="18" t="n">
+        <v>17100</v>
       </c>
     </row>
     <row r="141" ht="11" customHeight="true" outlineLevel="3">
       <c r="B141" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="C141" s="11" t="n">
-        <v>734</v>
+      <c r="C141" s="18" t="n">
+        <v>33604</v>
       </c>
     </row>
     <row r="142" ht="11" customHeight="true" outlineLevel="3">
@@ -3041,15 +2735,15 @@
         <v>141</v>
       </c>
       <c r="C142" s="11" t="n">
-        <v>377</v>
+        <v>100</v>
       </c>
     </row>
     <row r="143" ht="11" customHeight="true" outlineLevel="3">
       <c r="B143" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C143" s="11" t="n">
-        <v>5</v>
+      <c r="C143" s="18" t="n">
+        <v>1590</v>
       </c>
     </row>
     <row r="144" ht="11" customHeight="true" outlineLevel="3">
@@ -3057,7 +2751,7 @@
         <v>143</v>
       </c>
       <c r="C144" s="11" t="n">
-        <v>31</v>
+        <v>438</v>
       </c>
     </row>
     <row r="145" ht="11" customHeight="true" outlineLevel="3">
@@ -3065,7 +2759,7 @@
         <v>144</v>
       </c>
       <c r="C145" s="11" t="n">
-        <v>756</v>
+        <v>92</v>
       </c>
     </row>
     <row r="146" ht="11" customHeight="true" outlineLevel="3">
@@ -3073,39 +2767,39 @@
         <v>145</v>
       </c>
       <c r="C146" s="11" t="n">
-        <v>5</v>
+        <v>709</v>
       </c>
     </row>
     <row r="147" ht="11" customHeight="true" outlineLevel="3">
       <c r="B147" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="C147" s="18" t="n">
-        <v>10860</v>
+      <c r="C147" s="11" t="n">
+        <v>991</v>
       </c>
     </row>
     <row r="148" ht="11" customHeight="true" outlineLevel="3">
       <c r="B148" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="C148" s="18" t="n">
-        <v>12862</v>
-      </c>
-    </row>
-    <row r="149" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C148" s="11" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="149" ht="22" customHeight="true" outlineLevel="3">
       <c r="B149" s="17" t="s">
         <v>148</v>
       </c>
       <c r="C149" s="18" t="n">
-        <v>8460</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="150" ht="11" customHeight="true" outlineLevel="3">
       <c r="B150" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C150" s="18" t="n">
-        <v>4818</v>
+      <c r="C150" s="11" t="n">
+        <v>790</v>
       </c>
     </row>
     <row r="151" ht="11" customHeight="true" outlineLevel="3">
@@ -3113,31 +2807,31 @@
         <v>150</v>
       </c>
       <c r="C151" s="18" t="n">
-        <v>15578</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="152" ht="11" customHeight="true" outlineLevel="3">
       <c r="B152" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="C152" s="11" t="n">
-        <v>5</v>
+      <c r="C152" s="18" t="n">
+        <v>1891</v>
       </c>
     </row>
     <row r="153" ht="11" customHeight="true" outlineLevel="3">
       <c r="B153" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="C153" s="11" t="n">
-        <v>368</v>
+      <c r="C153" s="18" t="n">
+        <v>2366</v>
       </c>
     </row>
     <row r="154" ht="11" customHeight="true" outlineLevel="3">
       <c r="B154" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="C154" s="11" t="n">
-        <v>61</v>
+      <c r="C154" s="18" t="n">
+        <v>2354</v>
       </c>
     </row>
     <row r="155" ht="11" customHeight="true" outlineLevel="3">
@@ -3145,7 +2839,7 @@
         <v>154</v>
       </c>
       <c r="C155" s="11" t="n">
-        <v>255</v>
+        <v>490</v>
       </c>
     </row>
     <row r="156" ht="11" customHeight="true" outlineLevel="3">
@@ -3153,15 +2847,15 @@
         <v>155</v>
       </c>
       <c r="C156" s="11" t="n">
-        <v>308</v>
+        <v>760</v>
       </c>
     </row>
     <row r="157" ht="11" customHeight="true" outlineLevel="3">
       <c r="B157" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="C157" s="11" t="n">
-        <v>15</v>
+      <c r="C157" s="18" t="n">
+        <v>1602</v>
       </c>
     </row>
     <row r="158" ht="11" customHeight="true" outlineLevel="3">
@@ -3169,15 +2863,15 @@
         <v>157</v>
       </c>
       <c r="C158" s="11" t="n">
-        <v>196</v>
+        <v>922</v>
       </c>
     </row>
     <row r="159" ht="11" customHeight="true" outlineLevel="3">
       <c r="B159" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="C159" s="11" t="n">
-        <v>30</v>
+      <c r="C159" s="18" t="n">
+        <v>3118</v>
       </c>
     </row>
     <row r="160" ht="11" customHeight="true" outlineLevel="3">
@@ -3185,15 +2879,15 @@
         <v>159</v>
       </c>
       <c r="C160" s="11" t="n">
-        <v>704</v>
+        <v>37</v>
       </c>
     </row>
     <row r="161" ht="11" customHeight="true" outlineLevel="3">
       <c r="B161" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="C161" s="11" t="n">
-        <v>10</v>
+      <c r="C161" s="18" t="n">
+        <v>1371</v>
       </c>
     </row>
     <row r="162" ht="11" customHeight="true" outlineLevel="3">
@@ -3201,23 +2895,23 @@
         <v>161</v>
       </c>
       <c r="C162" s="11" t="n">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="163" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B163" s="17" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="163" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B163" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="C163" s="11" t="n">
-        <v>30</v>
+      <c r="C163" s="12" t="n">
+        <v>147670</v>
       </c>
     </row>
     <row r="164" ht="11" customHeight="true" outlineLevel="3">
       <c r="B164" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="C164" s="11" t="n">
-        <v>13</v>
+      <c r="C164" s="18" t="n">
+        <v>1370</v>
       </c>
     </row>
     <row r="165" ht="11" customHeight="true" outlineLevel="3">
@@ -3225,31 +2919,31 @@
         <v>164</v>
       </c>
       <c r="C165" s="11" t="n">
-        <v>26</v>
+        <v>255</v>
       </c>
     </row>
     <row r="166" ht="11" customHeight="true" outlineLevel="3">
       <c r="B166" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="C166" s="18" t="n">
-        <v>2058</v>
+      <c r="C166" s="11" t="n">
+        <v>266</v>
       </c>
     </row>
     <row r="167" ht="11" customHeight="true" outlineLevel="3">
       <c r="B167" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="C167" s="18" t="n">
-        <v>1269</v>
+      <c r="C167" s="11" t="n">
+        <v>715</v>
       </c>
     </row>
     <row r="168" ht="11" customHeight="true" outlineLevel="3">
       <c r="B168" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="C168" s="11" t="n">
-        <v>6</v>
+      <c r="C168" s="18" t="n">
+        <v>4162</v>
       </c>
     </row>
     <row r="169" ht="11" customHeight="true" outlineLevel="3">
@@ -3257,23 +2951,23 @@
         <v>168</v>
       </c>
       <c r="C169" s="11" t="n">
-        <v>925</v>
+        <v>641</v>
       </c>
     </row>
     <row r="170" ht="11" customHeight="true" outlineLevel="3">
       <c r="B170" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="C170" s="18" t="n">
-        <v>1898</v>
+      <c r="C170" s="11" t="n">
+        <v>376</v>
       </c>
     </row>
     <row r="171" ht="11" customHeight="true" outlineLevel="3">
       <c r="B171" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="C171" s="11" t="n">
-        <v>392</v>
+      <c r="C171" s="18" t="n">
+        <v>1286</v>
       </c>
     </row>
     <row r="172" ht="11" customHeight="true" outlineLevel="3">
@@ -3281,7 +2975,7 @@
         <v>171</v>
       </c>
       <c r="C172" s="11" t="n">
-        <v>562</v>
+        <v>816</v>
       </c>
     </row>
     <row r="173" ht="11" customHeight="true" outlineLevel="3">
@@ -3289,31 +2983,31 @@
         <v>172</v>
       </c>
       <c r="C173" s="11" t="n">
-        <v>669</v>
+        <v>490</v>
       </c>
     </row>
     <row r="174" ht="11" customHeight="true" outlineLevel="3">
       <c r="B174" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="C174" s="11" t="n">
-        <v>731</v>
+      <c r="C174" s="18" t="n">
+        <v>4397</v>
       </c>
     </row>
     <row r="175" ht="11" customHeight="true" outlineLevel="3">
       <c r="B175" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="C175" s="11" t="n">
-        <v>142</v>
+      <c r="C175" s="18" t="n">
+        <v>1242</v>
       </c>
     </row>
     <row r="176" ht="11" customHeight="true" outlineLevel="3">
       <c r="B176" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="C176" s="18" t="n">
-        <v>1864</v>
+      <c r="C176" s="11" t="n">
+        <v>871</v>
       </c>
     </row>
     <row r="177" ht="11" customHeight="true" outlineLevel="3">
@@ -3321,7 +3015,7 @@
         <v>176</v>
       </c>
       <c r="C177" s="11" t="n">
-        <v>16</v>
+        <v>511</v>
       </c>
     </row>
     <row r="178" ht="11" customHeight="true" outlineLevel="3">
@@ -3329,15 +3023,15 @@
         <v>177</v>
       </c>
       <c r="C178" s="11" t="n">
-        <v>40</v>
+        <v>400</v>
       </c>
     </row>
     <row r="179" ht="11" customHeight="true" outlineLevel="3">
       <c r="B179" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="C179" s="18" t="n">
-        <v>1049</v>
+      <c r="C179" s="11" t="n">
+        <v>426</v>
       </c>
     </row>
     <row r="180" ht="11" customHeight="true" outlineLevel="3">
@@ -3345,31 +3039,31 @@
         <v>179</v>
       </c>
       <c r="C180" s="11" t="n">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="181" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B181" s="16" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="181" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B181" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="C181" s="12" t="n">
-        <v>170377</v>
+      <c r="C181" s="18" t="n">
+        <v>1251</v>
       </c>
     </row>
     <row r="182" ht="11" customHeight="true" outlineLevel="3">
       <c r="B182" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="C182" s="18" t="n">
-        <v>1633</v>
+      <c r="C182" s="11" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="183" ht="11" customHeight="true" outlineLevel="3">
       <c r="B183" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="C183" s="11" t="n">
-        <v>289</v>
+      <c r="C183" s="18" t="n">
+        <v>1431</v>
       </c>
     </row>
     <row r="184" ht="11" customHeight="true" outlineLevel="3">
@@ -3377,7 +3071,7 @@
         <v>183</v>
       </c>
       <c r="C184" s="11" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="185" ht="11" customHeight="true" outlineLevel="3">
@@ -3385,7 +3079,7 @@
         <v>184</v>
       </c>
       <c r="C185" s="11" t="n">
-        <v>149</v>
+        <v>864</v>
       </c>
     </row>
     <row r="186" ht="11" customHeight="true" outlineLevel="3">
@@ -3393,31 +3087,31 @@
         <v>185</v>
       </c>
       <c r="C186" s="18" t="n">
-        <v>2624</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="187" ht="11" customHeight="true" outlineLevel="3">
       <c r="B187" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="C187" s="18" t="n">
-        <v>1341</v>
+      <c r="C187" s="11" t="n">
+        <v>-77</v>
       </c>
     </row>
     <row r="188" ht="11" customHeight="true" outlineLevel="3">
       <c r="B188" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="C188" s="11" t="n">
-        <v>599</v>
+      <c r="C188" s="18" t="n">
+        <v>3060</v>
       </c>
     </row>
     <row r="189" ht="11" customHeight="true" outlineLevel="3">
       <c r="B189" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="C189" s="11" t="n">
-        <v>701</v>
+      <c r="C189" s="18" t="n">
+        <v>1603</v>
       </c>
     </row>
     <row r="190" ht="11" customHeight="true" outlineLevel="3">
@@ -3425,7 +3119,7 @@
         <v>189</v>
       </c>
       <c r="C190" s="11" t="n">
-        <v>533</v>
+        <v>89</v>
       </c>
     </row>
     <row r="191" ht="11" customHeight="true" outlineLevel="3">
@@ -3433,23 +3127,23 @@
         <v>190</v>
       </c>
       <c r="C191" s="11" t="n">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="192" ht="11" customHeight="true" outlineLevel="3">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="192" ht="22" customHeight="true" outlineLevel="3">
       <c r="B192" s="17" t="s">
         <v>191</v>
       </c>
       <c r="C192" s="18" t="n">
-        <v>3815</v>
-      </c>
-    </row>
-    <row r="193" ht="11" customHeight="true" outlineLevel="3">
+        <v>20736</v>
+      </c>
+    </row>
+    <row r="193" ht="22" customHeight="true" outlineLevel="3">
       <c r="B193" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="C193" s="11" t="n">
-        <v>788</v>
+      <c r="C193" s="18" t="n">
+        <v>7819</v>
       </c>
     </row>
     <row r="194" ht="11" customHeight="true" outlineLevel="3">
@@ -3457,31 +3151,31 @@
         <v>193</v>
       </c>
       <c r="C194" s="11" t="n">
-        <v>407</v>
+        <v>522</v>
       </c>
     </row>
     <row r="195" ht="11" customHeight="true" outlineLevel="3">
       <c r="B195" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="C195" s="11" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="196" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C195" s="18" t="n">
+        <v>25007</v>
+      </c>
+    </row>
+    <row r="196" ht="22" customHeight="true" outlineLevel="3">
       <c r="B196" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="C196" s="11" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="197" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C196" s="18" t="n">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="197" ht="22" customHeight="true" outlineLevel="3">
       <c r="B197" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="C197" s="18" t="n">
-        <v>5252</v>
+      <c r="C197" s="11" t="n">
+        <v>298</v>
       </c>
     </row>
     <row r="198" ht="11" customHeight="true" outlineLevel="3">
@@ -3489,15 +3183,15 @@
         <v>197</v>
       </c>
       <c r="C198" s="11" t="n">
-        <v>111</v>
+        <v>577</v>
       </c>
     </row>
     <row r="199" ht="11" customHeight="true" outlineLevel="3">
       <c r="B199" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="C199" s="11" t="n">
-        <v>161</v>
+      <c r="C199" s="18" t="n">
+        <v>15017</v>
       </c>
     </row>
     <row r="200" ht="11" customHeight="true" outlineLevel="3">
@@ -3505,15 +3199,15 @@
         <v>199</v>
       </c>
       <c r="C200" s="11" t="n">
-        <v>568</v>
+        <v>296</v>
       </c>
     </row>
     <row r="201" ht="11" customHeight="true" outlineLevel="3">
       <c r="B201" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="C201" s="18" t="n">
-        <v>10811</v>
+      <c r="C201" s="11" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="202" ht="11" customHeight="true" outlineLevel="3">
@@ -3521,7 +3215,7 @@
         <v>201</v>
       </c>
       <c r="C202" s="11" t="n">
-        <v>342</v>
+        <v>444</v>
       </c>
     </row>
     <row r="203" ht="11" customHeight="true" outlineLevel="3">
@@ -3529,15 +3223,15 @@
         <v>202</v>
       </c>
       <c r="C203" s="11" t="n">
-        <v>430</v>
+        <v>161</v>
       </c>
     </row>
     <row r="204" ht="11" customHeight="true" outlineLevel="3">
       <c r="B204" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="C204" s="18" t="n">
-        <v>4626</v>
+      <c r="C204" s="11" t="n">
+        <v>556</v>
       </c>
     </row>
     <row r="205" ht="11" customHeight="true" outlineLevel="3">
@@ -3545,7 +3239,7 @@
         <v>204</v>
       </c>
       <c r="C205" s="11" t="n">
-        <v>290</v>
+        <v>608</v>
       </c>
     </row>
     <row r="206" ht="11" customHeight="true" outlineLevel="3">
@@ -3553,7 +3247,7 @@
         <v>205</v>
       </c>
       <c r="C206" s="11" t="n">
-        <v>130</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" ht="11" customHeight="true" outlineLevel="3">
@@ -3561,7 +3255,7 @@
         <v>206</v>
       </c>
       <c r="C207" s="11" t="n">
-        <v>192</v>
+        <v>430</v>
       </c>
     </row>
     <row r="208" ht="11" customHeight="true" outlineLevel="3">
@@ -3569,7 +3263,7 @@
         <v>207</v>
       </c>
       <c r="C208" s="18" t="n">
-        <v>10876</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="209" ht="11" customHeight="true" outlineLevel="3">
@@ -3577,23 +3271,23 @@
         <v>208</v>
       </c>
       <c r="C209" s="11" t="n">
-        <v>644</v>
+        <v>962</v>
       </c>
     </row>
     <row r="210" ht="11" customHeight="true" outlineLevel="3">
       <c r="B210" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="C210" s="11" t="n">
-        <v>734</v>
+      <c r="C210" s="18" t="n">
+        <v>1259</v>
       </c>
     </row>
     <row r="211" ht="11" customHeight="true" outlineLevel="3">
       <c r="B211" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="C211" s="11" t="n">
-        <v>285</v>
+      <c r="C211" s="18" t="n">
+        <v>1218</v>
       </c>
     </row>
     <row r="212" ht="11" customHeight="true" outlineLevel="3">
@@ -3601,7 +3295,7 @@
         <v>211</v>
       </c>
       <c r="C212" s="11" t="n">
-        <v>27</v>
+        <v>701</v>
       </c>
     </row>
     <row r="213" ht="11" customHeight="true" outlineLevel="3">
@@ -3609,7 +3303,7 @@
         <v>212</v>
       </c>
       <c r="C213" s="11" t="n">
-        <v>716</v>
+        <v>668</v>
       </c>
     </row>
     <row r="214" ht="11" customHeight="true" outlineLevel="3">
@@ -3617,7 +3311,7 @@
         <v>213</v>
       </c>
       <c r="C214" s="11" t="n">
-        <v>428</v>
+        <v>656</v>
       </c>
     </row>
     <row r="215" ht="11" customHeight="true" outlineLevel="3">
@@ -3625,31 +3319,31 @@
         <v>214</v>
       </c>
       <c r="C215" s="11" t="n">
-        <v>44</v>
+        <v>125</v>
       </c>
     </row>
     <row r="216" ht="11" customHeight="true" outlineLevel="3">
       <c r="B216" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="C216" s="11" t="n">
-        <v>486</v>
+      <c r="C216" s="18" t="n">
+        <v>1410</v>
       </c>
     </row>
     <row r="217" ht="11" customHeight="true" outlineLevel="3">
       <c r="B217" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="C217" s="11" t="n">
-        <v>54</v>
+      <c r="C217" s="18" t="n">
+        <v>2238</v>
       </c>
     </row>
     <row r="218" ht="11" customHeight="true" outlineLevel="3">
       <c r="B218" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="C218" s="18" t="n">
-        <v>3871</v>
+      <c r="C218" s="11" t="n">
+        <v>785</v>
       </c>
     </row>
     <row r="219" ht="11" customHeight="true" outlineLevel="3">
@@ -3657,15 +3351,15 @@
         <v>218</v>
       </c>
       <c r="C219" s="18" t="n">
-        <v>1182</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="220" ht="11" customHeight="true" outlineLevel="3">
       <c r="B220" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="C220" s="18" t="n">
-        <v>1789</v>
+      <c r="C220" s="11" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="221" ht="11" customHeight="true" outlineLevel="3">
@@ -3673,7 +3367,7 @@
         <v>220</v>
       </c>
       <c r="C221" s="11" t="n">
-        <v>190</v>
+        <v>234</v>
       </c>
     </row>
     <row r="222" ht="11" customHeight="true" outlineLevel="3">
@@ -3681,7 +3375,7 @@
         <v>221</v>
       </c>
       <c r="C222" s="18" t="n">
-        <v>2381</v>
+        <v>17231</v>
       </c>
     </row>
     <row r="223" ht="11" customHeight="true" outlineLevel="3">
@@ -3689,7 +3383,7 @@
         <v>222</v>
       </c>
       <c r="C223" s="11" t="n">
-        <v>277</v>
+        <v>382</v>
       </c>
     </row>
     <row r="224" ht="11" customHeight="true" outlineLevel="3">
@@ -3697,7 +3391,7 @@
         <v>223</v>
       </c>
       <c r="C224" s="18" t="n">
-        <v>1351</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="225" ht="11" customHeight="true" outlineLevel="3">
@@ -3705,31 +3399,31 @@
         <v>224</v>
       </c>
       <c r="C225" s="11" t="n">
-        <v>340</v>
+        <v>529</v>
       </c>
     </row>
     <row r="226" ht="11" customHeight="true" outlineLevel="3">
       <c r="B226" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="C226" s="11" t="n">
-        <v>353</v>
+      <c r="C226" s="18" t="n">
+        <v>1166</v>
       </c>
     </row>
     <row r="227" ht="11" customHeight="true" outlineLevel="3">
       <c r="B227" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="C227" s="11" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="228" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C227" s="18" t="n">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="228" ht="11" customHeight="true" outlineLevel="3">
       <c r="B228" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="C228" s="18" t="n">
-        <v>3713</v>
+      <c r="C228" s="11" t="n">
+        <v>416</v>
       </c>
     </row>
     <row r="229" ht="11" customHeight="true" outlineLevel="3">
@@ -3737,7 +3431,7 @@
         <v>228</v>
       </c>
       <c r="C229" s="11" t="n">
-        <v>293</v>
+        <v>201</v>
       </c>
     </row>
     <row r="230" ht="11" customHeight="true" outlineLevel="3">
@@ -3745,23 +3439,23 @@
         <v>229</v>
       </c>
       <c r="C230" s="11" t="n">
-        <v>80</v>
+        <v>748</v>
       </c>
     </row>
     <row r="231" ht="11" customHeight="true" outlineLevel="3">
       <c r="B231" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="C231" s="18" t="n">
-        <v>2509</v>
-      </c>
-    </row>
-    <row r="232" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C231" s="11" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="232" ht="11" customHeight="true" outlineLevel="3">
       <c r="B232" s="17" t="s">
         <v>231</v>
       </c>
       <c r="C232" s="18" t="n">
-        <v>1101</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="233" ht="11" customHeight="true" outlineLevel="3">
@@ -3769,23 +3463,23 @@
         <v>232</v>
       </c>
       <c r="C233" s="11" t="n">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="234" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B234" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B234" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="C234" s="11" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="235" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C234" s="12" t="n">
+        <v>75273</v>
+      </c>
+    </row>
+    <row r="235" ht="11" customHeight="true" outlineLevel="3">
       <c r="B235" s="17" t="s">
         <v>234</v>
       </c>
       <c r="C235" s="18" t="n">
-        <v>1786</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="236" ht="11" customHeight="true" outlineLevel="3">
@@ -3793,15 +3487,15 @@
         <v>235</v>
       </c>
       <c r="C236" s="11" t="n">
-        <v>602</v>
+        <v>462</v>
       </c>
     </row>
     <row r="237" ht="11" customHeight="true" outlineLevel="3">
       <c r="B237" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="C237" s="11" t="n">
-        <v>473</v>
+      <c r="C237" s="18" t="n">
+        <v>2796</v>
       </c>
     </row>
     <row r="238" ht="11" customHeight="true" outlineLevel="3">
@@ -3809,39 +3503,39 @@
         <v>237</v>
       </c>
       <c r="C238" s="11" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239" ht="11" customHeight="true" outlineLevel="3">
       <c r="B239" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="C239" s="11" t="n">
-        <v>374</v>
+      <c r="C239" s="18" t="n">
+        <v>1493</v>
       </c>
     </row>
     <row r="240" ht="11" customHeight="true" outlineLevel="3">
       <c r="B240" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="C240" s="11" t="n">
-        <v>237</v>
+      <c r="C240" s="18" t="n">
+        <v>1339</v>
       </c>
     </row>
     <row r="241" ht="11" customHeight="true" outlineLevel="3">
       <c r="B241" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="C241" s="11" t="n">
-        <v>38</v>
+      <c r="C241" s="18" t="n">
+        <v>6777</v>
       </c>
     </row>
     <row r="242" ht="11" customHeight="true" outlineLevel="3">
       <c r="B242" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="C242" s="18" t="n">
-        <v>10118</v>
+      <c r="C242" s="11" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="243" ht="11" customHeight="true" outlineLevel="3">
@@ -3849,7 +3543,7 @@
         <v>242</v>
       </c>
       <c r="C243" s="11" t="n">
-        <v>585</v>
+        <v>50</v>
       </c>
     </row>
     <row r="244" ht="11" customHeight="true" outlineLevel="3">
@@ -3857,7 +3551,7 @@
         <v>243</v>
       </c>
       <c r="C244" s="11" t="n">
-        <v>552</v>
+        <v>398</v>
       </c>
     </row>
     <row r="245" ht="11" customHeight="true" outlineLevel="3">
@@ -3865,15 +3559,15 @@
         <v>244</v>
       </c>
       <c r="C245" s="11" t="n">
-        <v>196</v>
+        <v>226</v>
       </c>
     </row>
     <row r="246" ht="11" customHeight="true" outlineLevel="3">
       <c r="B246" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="C246" s="18" t="n">
-        <v>5550</v>
+      <c r="C246" s="11" t="n">
+        <v>974</v>
       </c>
     </row>
     <row r="247" ht="11" customHeight="true" outlineLevel="3">
@@ -3881,23 +3575,23 @@
         <v>246</v>
       </c>
       <c r="C247" s="11" t="n">
-        <v>407</v>
+        <v>318</v>
       </c>
     </row>
     <row r="248" ht="11" customHeight="true" outlineLevel="3">
       <c r="B248" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="C248" s="11" t="n">
-        <v>512</v>
+      <c r="C248" s="18" t="n">
+        <v>2096</v>
       </c>
     </row>
     <row r="249" ht="11" customHeight="true" outlineLevel="3">
       <c r="B249" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="C249" s="11" t="n">
-        <v>20</v>
+      <c r="C249" s="18" t="n">
+        <v>1763</v>
       </c>
     </row>
     <row r="250" ht="11" customHeight="true" outlineLevel="3">
@@ -3905,7 +3599,7 @@
         <v>249</v>
       </c>
       <c r="C250" s="18" t="n">
-        <v>4115</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="251" ht="11" customHeight="true" outlineLevel="3">
@@ -3913,23 +3607,23 @@
         <v>250</v>
       </c>
       <c r="C251" s="18" t="n">
-        <v>2577</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="252" ht="11" customHeight="true" outlineLevel="3">
       <c r="B252" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="C252" s="11" t="n">
-        <v>428</v>
+      <c r="C252" s="18" t="n">
+        <v>1565</v>
       </c>
     </row>
     <row r="253" ht="11" customHeight="true" outlineLevel="3">
       <c r="B253" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="C253" s="18" t="n">
-        <v>2957</v>
+      <c r="C253" s="11" t="n">
+        <v>321</v>
       </c>
     </row>
     <row r="254" ht="11" customHeight="true" outlineLevel="3">
@@ -3937,15 +3631,15 @@
         <v>253</v>
       </c>
       <c r="C254" s="11" t="n">
-        <v>54</v>
+        <v>981</v>
       </c>
     </row>
     <row r="255" ht="11" customHeight="true" outlineLevel="3">
       <c r="B255" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="C255" s="11" t="n">
-        <v>578</v>
+      <c r="C255" s="18" t="n">
+        <v>1394</v>
       </c>
     </row>
     <row r="256" ht="11" customHeight="true" outlineLevel="3">
@@ -3953,7 +3647,7 @@
         <v>255</v>
       </c>
       <c r="C256" s="11" t="n">
-        <v>189</v>
+        <v>434</v>
       </c>
     </row>
     <row r="257" ht="11" customHeight="true" outlineLevel="3">
@@ -3961,15 +3655,15 @@
         <v>256</v>
       </c>
       <c r="C257" s="18" t="n">
-        <v>2915</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="258" ht="11" customHeight="true" outlineLevel="3">
       <c r="B258" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="C258" s="11" t="n">
-        <v>441</v>
+      <c r="C258" s="18" t="n">
+        <v>2094</v>
       </c>
     </row>
     <row r="259" ht="11" customHeight="true" outlineLevel="3">
@@ -3977,15 +3671,15 @@
         <v>258</v>
       </c>
       <c r="C259" s="18" t="n">
-        <v>1898</v>
+        <v>4659</v>
       </c>
     </row>
     <row r="260" ht="11" customHeight="true" outlineLevel="3">
       <c r="B260" s="17" t="s">
         <v>259</v>
       </c>
-      <c r="C260" s="11" t="n">
-        <v>462</v>
+      <c r="C260" s="18" t="n">
+        <v>3289</v>
       </c>
     </row>
     <row r="261" ht="11" customHeight="true" outlineLevel="3">
@@ -3993,23 +3687,23 @@
         <v>260</v>
       </c>
       <c r="C261" s="18" t="n">
-        <v>3279</v>
+        <v>4344</v>
       </c>
     </row>
     <row r="262" ht="11" customHeight="true" outlineLevel="3">
       <c r="B262" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="C262" s="11" t="n">
-        <v>331</v>
+      <c r="C262" s="18" t="n">
+        <v>4597</v>
       </c>
     </row>
     <row r="263" ht="11" customHeight="true" outlineLevel="3">
       <c r="B263" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="C263" s="11" t="n">
-        <v>861</v>
+      <c r="C263" s="18" t="n">
+        <v>1755</v>
       </c>
     </row>
     <row r="264" ht="11" customHeight="true" outlineLevel="3">
@@ -4017,15 +3711,15 @@
         <v>263</v>
       </c>
       <c r="C264" s="18" t="n">
-        <v>4911</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="265" ht="11" customHeight="true" outlineLevel="3">
       <c r="B265" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="C265" s="11" t="n">
-        <v>626</v>
+      <c r="C265" s="18" t="n">
+        <v>3346</v>
       </c>
     </row>
     <row r="266" ht="11" customHeight="true" outlineLevel="3">
@@ -4033,7 +3727,7 @@
         <v>265</v>
       </c>
       <c r="C266" s="18" t="n">
-        <v>1725</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="267" ht="11" customHeight="true" outlineLevel="3">
@@ -4041,39 +3735,39 @@
         <v>266</v>
       </c>
       <c r="C267" s="18" t="n">
-        <v>20217</v>
+        <v>4605</v>
       </c>
     </row>
     <row r="268" ht="11" customHeight="true" outlineLevel="3">
       <c r="B268" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="C268" s="11" t="n">
-        <v>310</v>
+      <c r="C268" s="18" t="n">
+        <v>2845</v>
       </c>
     </row>
     <row r="269" ht="11" customHeight="true" outlineLevel="3">
       <c r="B269" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="C269" s="11" t="n">
-        <v>269</v>
+      <c r="C269" s="18" t="n">
+        <v>6236</v>
       </c>
     </row>
     <row r="270" ht="11" customHeight="true" outlineLevel="3">
       <c r="B270" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="C270" s="11" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="271" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B271" s="17" t="s">
+      <c r="C270" s="18" t="n">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="271" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B271" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="C271" s="18" t="n">
-        <v>4897</v>
+      <c r="C271" s="12" t="n">
+        <v>5857</v>
       </c>
     </row>
     <row r="272" ht="11" customHeight="true" outlineLevel="3">
@@ -4081,31 +3775,31 @@
         <v>271</v>
       </c>
       <c r="C272" s="11" t="n">
-        <v>224</v>
+        <v>272</v>
       </c>
     </row>
     <row r="273" ht="11" customHeight="true" outlineLevel="3">
       <c r="B273" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="C273" s="18" t="n">
-        <v>1780</v>
+      <c r="C273" s="11" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="274" ht="11" customHeight="true" outlineLevel="3">
       <c r="B274" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="C274" s="18" t="n">
-        <v>3955</v>
+      <c r="C274" s="11" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="275" ht="11" customHeight="true" outlineLevel="3">
       <c r="B275" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="C275" s="18" t="n">
-        <v>3124</v>
+      <c r="C275" s="11" t="n">
+        <v>498</v>
       </c>
     </row>
     <row r="276" ht="11" customHeight="true" outlineLevel="3">
@@ -4113,31 +3807,31 @@
         <v>275</v>
       </c>
       <c r="C276" s="11" t="n">
-        <v>476</v>
+        <v>78</v>
       </c>
     </row>
     <row r="277" ht="11" customHeight="true" outlineLevel="3">
       <c r="B277" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="C277" s="18" t="n">
-        <v>4574</v>
+      <c r="C277" s="11" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="278" ht="11" customHeight="true" outlineLevel="3">
       <c r="B278" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="C278" s="18" t="n">
-        <v>4696</v>
+      <c r="C278" s="11" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="279" ht="11" customHeight="true" outlineLevel="3">
       <c r="B279" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="C279" s="18" t="n">
-        <v>4755</v>
+      <c r="C279" s="11" t="n">
+        <v>194</v>
       </c>
     </row>
     <row r="280" ht="11" customHeight="true" outlineLevel="3">
@@ -4145,23 +3839,23 @@
         <v>279</v>
       </c>
       <c r="C280" s="11" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="281" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B281" s="16" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="281" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B281" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="C281" s="12" t="n">
-        <v>75193</v>
+      <c r="C281" s="11" t="n">
+        <v>569</v>
       </c>
     </row>
     <row r="282" ht="11" customHeight="true" outlineLevel="3">
       <c r="B282" s="17" t="s">
         <v>281</v>
       </c>
-      <c r="C282" s="18" t="n">
-        <v>1510</v>
+      <c r="C282" s="11" t="n">
+        <v>661</v>
       </c>
     </row>
     <row r="283" ht="11" customHeight="true" outlineLevel="3">
@@ -4169,15 +3863,15 @@
         <v>282</v>
       </c>
       <c r="C283" s="11" t="n">
-        <v>688</v>
+        <v>345</v>
       </c>
     </row>
     <row r="284" ht="11" customHeight="true" outlineLevel="3">
       <c r="B284" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="C284" s="18" t="n">
-        <v>2036</v>
+      <c r="C284" s="11" t="n">
+        <v>258</v>
       </c>
     </row>
     <row r="285" ht="11" customHeight="true" outlineLevel="3">
@@ -4192,24 +3886,24 @@
       <c r="B286" s="17" t="s">
         <v>285</v>
       </c>
-      <c r="C286" s="18" t="n">
-        <v>1103</v>
+      <c r="C286" s="11" t="n">
+        <v>455</v>
       </c>
     </row>
     <row r="287" ht="11" customHeight="true" outlineLevel="3">
       <c r="B287" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="C287" s="18" t="n">
-        <v>1528</v>
+      <c r="C287" s="11" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="288" ht="11" customHeight="true" outlineLevel="3">
       <c r="B288" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="C288" s="18" t="n">
-        <v>8636</v>
+      <c r="C288" s="11" t="n">
+        <v>960</v>
       </c>
     </row>
     <row r="289" ht="11" customHeight="true" outlineLevel="3">
@@ -4217,7 +3911,7 @@
         <v>288</v>
       </c>
       <c r="C289" s="11" t="n">
-        <v>67</v>
+        <v>22</v>
       </c>
     </row>
     <row r="290" ht="11" customHeight="true" outlineLevel="3">
@@ -4225,7 +3919,7 @@
         <v>289</v>
       </c>
       <c r="C290" s="11" t="n">
-        <v>50</v>
+        <v>557</v>
       </c>
     </row>
     <row r="291" ht="11" customHeight="true" outlineLevel="3">
@@ -4233,7 +3927,7 @@
         <v>290</v>
       </c>
       <c r="C291" s="11" t="n">
-        <v>345</v>
+        <v>7</v>
       </c>
     </row>
     <row r="292" ht="11" customHeight="true" outlineLevel="3">
@@ -4241,15 +3935,15 @@
         <v>291</v>
       </c>
       <c r="C292" s="11" t="n">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="293" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B293" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="293" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B293" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="C293" s="11" t="n">
-        <v>976</v>
+      <c r="C293" s="12" t="n">
+        <v>63144</v>
       </c>
     </row>
     <row r="294" ht="11" customHeight="true" outlineLevel="3">
@@ -4257,7 +3951,7 @@
         <v>293</v>
       </c>
       <c r="C294" s="11" t="n">
-        <v>7</v>
+        <v>429</v>
       </c>
     </row>
     <row r="295" ht="11" customHeight="true" outlineLevel="3">
@@ -4265,47 +3959,47 @@
         <v>294</v>
       </c>
       <c r="C295" s="11" t="n">
-        <v>364</v>
+        <v>990</v>
       </c>
     </row>
     <row r="296" ht="11" customHeight="true" outlineLevel="3">
       <c r="B296" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="C296" s="18" t="n">
-        <v>2664</v>
+      <c r="C296" s="11" t="n">
+        <v>340</v>
       </c>
     </row>
     <row r="297" ht="11" customHeight="true" outlineLevel="3">
       <c r="B297" s="17" t="s">
         <v>296</v>
       </c>
-      <c r="C297" s="18" t="n">
-        <v>3842</v>
+      <c r="C297" s="11" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="298" ht="11" customHeight="true" outlineLevel="3">
       <c r="B298" s="17" t="s">
         <v>297</v>
       </c>
-      <c r="C298" s="18" t="n">
-        <v>3251</v>
+      <c r="C298" s="11" t="n">
+        <v>269</v>
       </c>
     </row>
     <row r="299" ht="11" customHeight="true" outlineLevel="3">
       <c r="B299" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="C299" s="18" t="n">
-        <v>1114</v>
+      <c r="C299" s="11" t="n">
+        <v>151</v>
       </c>
     </row>
     <row r="300" ht="11" customHeight="true" outlineLevel="3">
       <c r="B300" s="17" t="s">
         <v>299</v>
       </c>
-      <c r="C300" s="18" t="n">
-        <v>2050</v>
+      <c r="C300" s="11" t="n">
+        <v>775</v>
       </c>
     </row>
     <row r="301" ht="11" customHeight="true" outlineLevel="3">
@@ -4313,7 +4007,7 @@
         <v>300</v>
       </c>
       <c r="C301" s="11" t="n">
-        <v>825</v>
+        <v>604</v>
       </c>
     </row>
     <row r="302" ht="11" customHeight="true" outlineLevel="3">
@@ -4321,39 +4015,39 @@
         <v>301</v>
       </c>
       <c r="C302" s="11" t="n">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="303" ht="11" customHeight="true" outlineLevel="3">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="303" ht="22" customHeight="true" outlineLevel="3">
       <c r="B303" s="17" t="s">
         <v>302</v>
       </c>
-      <c r="C303" s="18" t="n">
-        <v>1631</v>
+      <c r="C303" s="11" t="n">
+        <v>215</v>
       </c>
     </row>
     <row r="304" ht="11" customHeight="true" outlineLevel="3">
       <c r="B304" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="C304" s="18" t="n">
-        <v>1245</v>
+      <c r="C304" s="11" t="n">
+        <v>451</v>
       </c>
     </row>
     <row r="305" ht="11" customHeight="true" outlineLevel="3">
       <c r="B305" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="C305" s="18" t="n">
-        <v>3141</v>
+      <c r="C305" s="11" t="n">
+        <v>188</v>
       </c>
     </row>
     <row r="306" ht="11" customHeight="true" outlineLevel="3">
       <c r="B306" s="17" t="s">
         <v>305</v>
       </c>
-      <c r="C306" s="18" t="n">
-        <v>3319</v>
+      <c r="C306" s="11" t="n">
+        <v>657</v>
       </c>
     </row>
     <row r="307" ht="11" customHeight="true" outlineLevel="3">
@@ -4361,103 +4055,103 @@
         <v>306</v>
       </c>
       <c r="C307" s="18" t="n">
-        <v>3975</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="308" ht="11" customHeight="true" outlineLevel="3">
       <c r="B308" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="C308" s="18" t="n">
-        <v>2227</v>
-      </c>
-    </row>
-    <row r="309" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C308" s="11" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="309" ht="22" customHeight="true" outlineLevel="3">
       <c r="B309" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="C309" s="18" t="n">
-        <v>2808</v>
-      </c>
-    </row>
-    <row r="310" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C309" s="11" t="n">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="310" ht="22" customHeight="true" outlineLevel="3">
       <c r="B310" s="17" t="s">
         <v>309</v>
       </c>
-      <c r="C310" s="18" t="n">
-        <v>3427</v>
-      </c>
-    </row>
-    <row r="311" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C310" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="311" ht="22" customHeight="true" outlineLevel="3">
       <c r="B311" s="17" t="s">
         <v>310</v>
       </c>
       <c r="C311" s="18" t="n">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="312" ht="11" customHeight="true" outlineLevel="3">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="312" ht="22" customHeight="true" outlineLevel="3">
       <c r="B312" s="17" t="s">
         <v>311</v>
       </c>
       <c r="C312" s="11" t="n">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="313" ht="11" customHeight="true" outlineLevel="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="313" ht="22" customHeight="true" outlineLevel="3">
       <c r="B313" s="17" t="s">
         <v>312</v>
       </c>
       <c r="C313" s="18" t="n">
-        <v>4982</v>
-      </c>
-    </row>
-    <row r="314" ht="11" customHeight="true" outlineLevel="3">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="314" ht="22" customHeight="true" outlineLevel="3">
       <c r="B314" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="C314" s="18" t="n">
-        <v>2103</v>
-      </c>
-    </row>
-    <row r="315" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C314" s="11" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="315" ht="22" customHeight="true" outlineLevel="3">
       <c r="B315" s="17" t="s">
         <v>314</v>
       </c>
-      <c r="C315" s="18" t="n">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="316" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C315" s="11" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="316" ht="22" customHeight="true" outlineLevel="3">
       <c r="B316" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="C316" s="18" t="n">
-        <v>1356</v>
+      <c r="C316" s="11" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="317" ht="11" customHeight="true" outlineLevel="3">
       <c r="B317" s="17" t="s">
         <v>316</v>
       </c>
-      <c r="C317" s="18" t="n">
-        <v>7764</v>
+      <c r="C317" s="11" t="n">
+        <v>657</v>
       </c>
     </row>
     <row r="318" ht="11" customHeight="true" outlineLevel="3">
       <c r="B318" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="C318" s="18" t="n">
-        <v>1441</v>
-      </c>
-    </row>
-    <row r="319" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B319" s="16" t="s">
+      <c r="C318" s="11" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="319" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B319" s="17" t="s">
         <v>318</v>
       </c>
-      <c r="C319" s="12" t="n">
-        <v>5928</v>
+      <c r="C319" s="11" t="n">
+        <v>928</v>
       </c>
     </row>
     <row r="320" ht="11" customHeight="true" outlineLevel="3">
@@ -4465,23 +4159,23 @@
         <v>319</v>
       </c>
       <c r="C320" s="11" t="n">
-        <v>781</v>
+        <v>148</v>
       </c>
     </row>
     <row r="321" ht="11" customHeight="true" outlineLevel="3">
       <c r="B321" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="C321" s="11" t="n">
-        <v>374</v>
+      <c r="C321" s="18" t="n">
+        <v>2601</v>
       </c>
     </row>
     <row r="322" ht="11" customHeight="true" outlineLevel="3">
       <c r="B322" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="C322" s="11" t="n">
-        <v>157</v>
+      <c r="C322" s="18" t="n">
+        <v>2570</v>
       </c>
     </row>
     <row r="323" ht="11" customHeight="true" outlineLevel="3">
@@ -4489,15 +4183,15 @@
         <v>322</v>
       </c>
       <c r="C323" s="11" t="n">
-        <v>392</v>
+        <v>765</v>
       </c>
     </row>
     <row r="324" ht="11" customHeight="true" outlineLevel="3">
       <c r="B324" s="17" t="s">
         <v>323</v>
       </c>
-      <c r="C324" s="11" t="n">
-        <v>39</v>
+      <c r="C324" s="18" t="n">
+        <v>1960</v>
       </c>
     </row>
     <row r="325" ht="11" customHeight="true" outlineLevel="3">
@@ -4505,23 +4199,23 @@
         <v>324</v>
       </c>
       <c r="C325" s="11" t="n">
-        <v>397</v>
+        <v>741</v>
       </c>
     </row>
     <row r="326" ht="11" customHeight="true" outlineLevel="3">
       <c r="B326" s="17" t="s">
         <v>325</v>
       </c>
-      <c r="C326" s="11" t="n">
-        <v>59</v>
+      <c r="C326" s="18" t="n">
+        <v>1940</v>
       </c>
     </row>
     <row r="327" ht="11" customHeight="true" outlineLevel="3">
       <c r="B327" s="17" t="s">
         <v>326</v>
       </c>
-      <c r="C327" s="11" t="n">
-        <v>209</v>
+      <c r="C327" s="18" t="n">
+        <v>4702</v>
       </c>
     </row>
     <row r="328" ht="11" customHeight="true" outlineLevel="3">
@@ -4529,31 +4223,31 @@
         <v>327</v>
       </c>
       <c r="C328" s="11" t="n">
-        <v>124</v>
+        <v>7</v>
       </c>
     </row>
     <row r="329" ht="11" customHeight="true" outlineLevel="3">
       <c r="B329" s="17" t="s">
         <v>328</v>
       </c>
-      <c r="C329" s="11" t="n">
-        <v>734</v>
+      <c r="C329" s="18" t="n">
+        <v>3628</v>
       </c>
     </row>
     <row r="330" ht="11" customHeight="true" outlineLevel="3">
       <c r="B330" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="C330" s="11" t="n">
-        <v>30</v>
+      <c r="C330" s="18" t="n">
+        <v>21479</v>
       </c>
     </row>
     <row r="331" ht="11" customHeight="true" outlineLevel="3">
       <c r="B331" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="C331" s="11" t="n">
-        <v>214</v>
+      <c r="C331" s="18" t="n">
+        <v>1151</v>
       </c>
     </row>
     <row r="332" ht="11" customHeight="true" outlineLevel="3">
@@ -4561,31 +4255,31 @@
         <v>331</v>
       </c>
       <c r="C332" s="11" t="n">
-        <v>376</v>
+        <v>194</v>
       </c>
     </row>
     <row r="333" ht="11" customHeight="true" outlineLevel="3">
       <c r="B333" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="C333" s="11" t="n">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="334" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B334" s="17" t="s">
+      <c r="C333" s="18" t="n">
+        <v>7716</v>
+      </c>
+    </row>
+    <row r="334" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B334" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="C334" s="11" t="n">
-        <v>398</v>
+      <c r="C334" s="12" t="n">
+        <v>69209</v>
       </c>
     </row>
     <row r="335" ht="11" customHeight="true" outlineLevel="3">
       <c r="B335" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="C335" s="11" t="n">
-        <v>409</v>
+      <c r="C335" s="18" t="n">
+        <v>1745</v>
       </c>
     </row>
     <row r="336" ht="11" customHeight="true" outlineLevel="3">
@@ -4593,31 +4287,31 @@
         <v>335</v>
       </c>
       <c r="C336" s="11" t="n">
-        <v>153</v>
+        <v>281</v>
       </c>
     </row>
     <row r="337" ht="11" customHeight="true" outlineLevel="3">
       <c r="B337" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="C337" s="11" t="n">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="338" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C337" s="18" t="n">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="338" ht="22" customHeight="true" outlineLevel="3">
       <c r="B338" s="17" t="s">
         <v>337</v>
       </c>
       <c r="C338" s="11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="339" ht="11" customHeight="true" outlineLevel="3">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="339" ht="22" customHeight="true" outlineLevel="3">
       <c r="B339" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="C339" s="11" t="n">
-        <v>17</v>
+      <c r="C339" s="18" t="n">
+        <v>1183</v>
       </c>
     </row>
     <row r="340" ht="11" customHeight="true" outlineLevel="3">
@@ -4625,7 +4319,7 @@
         <v>339</v>
       </c>
       <c r="C340" s="11" t="n">
-        <v>12</v>
+        <v>527</v>
       </c>
     </row>
     <row r="341" ht="11" customHeight="true" outlineLevel="3">
@@ -4633,23 +4327,23 @@
         <v>340</v>
       </c>
       <c r="C341" s="11" t="n">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="342" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B342" s="16" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="342" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B342" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="C342" s="12" t="n">
-        <v>56065</v>
+      <c r="C342" s="11" t="n">
+        <v>958</v>
       </c>
     </row>
     <row r="343" ht="11" customHeight="true" outlineLevel="3">
       <c r="B343" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="C343" s="11" t="n">
-        <v>516</v>
+      <c r="C343" s="18" t="n">
+        <v>2786</v>
       </c>
     </row>
     <row r="344" ht="11" customHeight="true" outlineLevel="3">
@@ -4657,15 +4351,15 @@
         <v>343</v>
       </c>
       <c r="C344" s="11" t="n">
-        <v>47</v>
+        <v>708</v>
       </c>
     </row>
     <row r="345" ht="11" customHeight="true" outlineLevel="3">
       <c r="B345" s="17" t="s">
         <v>344</v>
       </c>
-      <c r="C345" s="11" t="n">
-        <v>283</v>
+      <c r="C345" s="18" t="n">
+        <v>1092</v>
       </c>
     </row>
     <row r="346" ht="11" customHeight="true" outlineLevel="3">
@@ -4673,7 +4367,7 @@
         <v>345</v>
       </c>
       <c r="C346" s="11" t="n">
-        <v>212</v>
+        <v>436</v>
       </c>
     </row>
     <row r="347" ht="11" customHeight="true" outlineLevel="3">
@@ -4681,7 +4375,7 @@
         <v>346</v>
       </c>
       <c r="C347" s="11" t="n">
-        <v>480</v>
+        <v>78</v>
       </c>
     </row>
     <row r="348" ht="11" customHeight="true" outlineLevel="3">
@@ -4689,7 +4383,7 @@
         <v>347</v>
       </c>
       <c r="C348" s="11" t="n">
-        <v>220</v>
+        <v>754</v>
       </c>
     </row>
     <row r="349" ht="11" customHeight="true" outlineLevel="3">
@@ -4697,15 +4391,15 @@
         <v>348</v>
       </c>
       <c r="C349" s="11" t="n">
-        <v>561</v>
+        <v>295</v>
       </c>
     </row>
     <row r="350" ht="11" customHeight="true" outlineLevel="3">
       <c r="B350" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="C350" s="11" t="n">
-        <v>281</v>
+      <c r="C350" s="18" t="n">
+        <v>1143</v>
       </c>
     </row>
     <row r="351" ht="11" customHeight="true" outlineLevel="3">
@@ -4713,7 +4407,7 @@
         <v>350</v>
       </c>
       <c r="C351" s="11" t="n">
-        <v>491</v>
+        <v>703</v>
       </c>
     </row>
     <row r="352" ht="11" customHeight="true" outlineLevel="3">
@@ -4721,7 +4415,7 @@
         <v>351</v>
       </c>
       <c r="C352" s="11" t="n">
-        <v>489</v>
+        <v>926</v>
       </c>
     </row>
     <row r="353" ht="11" customHeight="true" outlineLevel="3">
@@ -4729,15 +4423,15 @@
         <v>352</v>
       </c>
       <c r="C353" s="11" t="n">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="354" ht="22" customHeight="true" outlineLevel="3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="354" ht="11" customHeight="true" outlineLevel="3">
       <c r="B354" s="17" t="s">
         <v>353</v>
       </c>
-      <c r="C354" s="11" t="n">
-        <v>410</v>
+      <c r="C354" s="18" t="n">
+        <v>1155</v>
       </c>
     </row>
     <row r="355" ht="11" customHeight="true" outlineLevel="3">
@@ -4745,15 +4439,15 @@
         <v>354</v>
       </c>
       <c r="C355" s="11" t="n">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="356" ht="22" customHeight="true" outlineLevel="3">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="356" ht="11" customHeight="true" outlineLevel="3">
       <c r="B356" s="17" t="s">
         <v>355</v>
       </c>
       <c r="C356" s="11" t="n">
-        <v>4</v>
+        <v>784</v>
       </c>
     </row>
     <row r="357" ht="11" customHeight="true" outlineLevel="3">
@@ -4761,7 +4455,7 @@
         <v>356</v>
       </c>
       <c r="C357" s="11" t="n">
-        <v>455</v>
+        <v>130</v>
       </c>
     </row>
     <row r="358" ht="11" customHeight="true" outlineLevel="3">
@@ -4769,7 +4463,7 @@
         <v>357</v>
       </c>
       <c r="C358" s="18" t="n">
-        <v>1560</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="359" ht="11" customHeight="true" outlineLevel="3">
@@ -4777,15 +4471,15 @@
         <v>358</v>
       </c>
       <c r="C359" s="18" t="n">
-        <v>1707</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="360" ht="11" customHeight="true" outlineLevel="3">
       <c r="B360" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="C360" s="18" t="n">
-        <v>1571</v>
+      <c r="C360" s="11" t="n">
+        <v>172</v>
       </c>
     </row>
     <row r="361" ht="11" customHeight="true" outlineLevel="3">
@@ -4793,15 +4487,15 @@
         <v>360</v>
       </c>
       <c r="C361" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="362" ht="22" customHeight="true" outlineLevel="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="362" ht="11" customHeight="true" outlineLevel="3">
       <c r="B362" s="17" t="s">
         <v>361</v>
       </c>
       <c r="C362" s="11" t="n">
-        <v>293</v>
+        <v>104</v>
       </c>
     </row>
     <row r="363" ht="22" customHeight="true" outlineLevel="3">
@@ -4812,12 +4506,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="364" ht="22" customHeight="true" outlineLevel="3">
+    <row r="364" ht="11" customHeight="true" outlineLevel="3">
       <c r="B364" s="17" t="s">
         <v>363</v>
       </c>
       <c r="C364" s="11" t="n">
-        <v>21</v>
+        <v>164</v>
       </c>
     </row>
     <row r="365" ht="22" customHeight="true" outlineLevel="3">
@@ -4825,15 +4519,15 @@
         <v>364</v>
       </c>
       <c r="C365" s="11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="366" ht="22" customHeight="true" outlineLevel="3">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="366" ht="11" customHeight="true" outlineLevel="3">
       <c r="B366" s="17" t="s">
         <v>365</v>
       </c>
       <c r="C366" s="11" t="n">
-        <v>608</v>
+        <v>186</v>
       </c>
     </row>
     <row r="367" ht="22" customHeight="true" outlineLevel="3">
@@ -4841,15 +4535,15 @@
         <v>366</v>
       </c>
       <c r="C367" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="368" ht="22" customHeight="true" outlineLevel="3">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="368" ht="11" customHeight="true" outlineLevel="3">
       <c r="B368" s="17" t="s">
         <v>367</v>
       </c>
       <c r="C368" s="11" t="n">
-        <v>7</v>
+        <v>270</v>
       </c>
     </row>
     <row r="369" ht="22" customHeight="true" outlineLevel="3">
@@ -4857,15 +4551,15 @@
         <v>368</v>
       </c>
       <c r="C369" s="11" t="n">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="370" ht="22" customHeight="true" outlineLevel="3">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="370" ht="11" customHeight="true" outlineLevel="3">
       <c r="B370" s="17" t="s">
         <v>369</v>
       </c>
-      <c r="C370" s="11" t="n">
-        <v>82</v>
+      <c r="C370" s="18" t="n">
+        <v>11999</v>
       </c>
     </row>
     <row r="371" ht="11" customHeight="true" outlineLevel="3">
@@ -4873,7 +4567,7 @@
         <v>370</v>
       </c>
       <c r="C371" s="11" t="n">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="372" ht="11" customHeight="true" outlineLevel="3">
@@ -4881,31 +4575,31 @@
         <v>371</v>
       </c>
       <c r="C372" s="11" t="n">
-        <v>32</v>
+        <v>299</v>
       </c>
     </row>
     <row r="373" ht="11" customHeight="true" outlineLevel="3">
       <c r="B373" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="C373" s="11" t="n">
-        <v>427</v>
+      <c r="C373" s="18" t="n">
+        <v>17694</v>
       </c>
     </row>
     <row r="374" ht="11" customHeight="true" outlineLevel="3">
       <c r="B374" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="C374" s="11" t="n">
-        <v>11</v>
+      <c r="C374" s="18" t="n">
+        <v>7860</v>
       </c>
     </row>
     <row r="375" ht="11" customHeight="true" outlineLevel="3">
       <c r="B375" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="C375" s="11" t="n">
-        <v>20</v>
+      <c r="C375" s="18" t="n">
+        <v>2823</v>
       </c>
     </row>
     <row r="376" ht="11" customHeight="true" outlineLevel="3">
@@ -4913,7 +4607,7 @@
         <v>375</v>
       </c>
       <c r="C376" s="11" t="n">
-        <v>674</v>
+        <v>10</v>
       </c>
     </row>
     <row r="377" ht="11" customHeight="true" outlineLevel="3">
@@ -4921,199 +4615,199 @@
         <v>376</v>
       </c>
       <c r="C377" s="11" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="378" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B378" s="17" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="378" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B378" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="C378" s="11" t="n">
-        <v>290</v>
+      <c r="C378" s="14" t="n">
+        <v>880</v>
       </c>
     </row>
     <row r="379" ht="11" customHeight="true" outlineLevel="3">
       <c r="B379" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="C379" s="18" t="n">
-        <v>3812</v>
-      </c>
-    </row>
-    <row r="380" ht="22" customHeight="true" outlineLevel="3">
+      <c r="C379" s="11" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="380" ht="11" customHeight="true" outlineLevel="3">
       <c r="B380" s="17" t="s">
         <v>379</v>
       </c>
       <c r="C380" s="11" t="n">
-        <v>202</v>
+        <v>85</v>
       </c>
     </row>
     <row r="381" ht="11" customHeight="true" outlineLevel="3">
       <c r="B381" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="C381" s="18" t="n">
-        <v>2727</v>
+      <c r="C381" s="11" t="n">
+        <v>295</v>
       </c>
     </row>
     <row r="382" ht="11" customHeight="true" outlineLevel="3">
       <c r="B382" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="C382" s="18" t="n">
-        <v>2378</v>
-      </c>
-    </row>
-    <row r="383" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B383" s="17" t="s">
+      <c r="C382" s="11" t="n">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="383" ht="11" customHeight="true" outlineLevel="2">
+      <c r="B383" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="C383" s="11" t="n">
-        <v>138</v>
+      <c r="C383" s="12" t="n">
+        <v>61838</v>
       </c>
     </row>
     <row r="384" ht="11" customHeight="true" outlineLevel="3">
       <c r="B384" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="C384" s="18" t="n">
-        <v>1032</v>
+      <c r="C384" s="11" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="385" ht="11" customHeight="true" outlineLevel="3">
       <c r="B385" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="C385" s="18" t="n">
-        <v>2321</v>
-      </c>
-    </row>
-    <row r="386" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C385" s="11" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="386" ht="22" customHeight="true" outlineLevel="3">
       <c r="B386" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="C386" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="387" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C386" s="18" t="n">
+        <v>3362</v>
+      </c>
+    </row>
+    <row r="387" ht="22" customHeight="true" outlineLevel="3">
       <c r="B387" s="17" t="s">
         <v>386</v>
       </c>
       <c r="C387" s="18" t="n">
-        <v>4761</v>
-      </c>
-    </row>
-    <row r="388" ht="11" customHeight="true" outlineLevel="3">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="388" ht="22" customHeight="true" outlineLevel="3">
       <c r="B388" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="C388" s="18" t="n">
-        <v>15682</v>
-      </c>
-    </row>
-    <row r="389" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C388" s="11" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="389" ht="22" customHeight="true" outlineLevel="3">
       <c r="B389" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="C389" s="18" t="n">
-        <v>3077</v>
+      <c r="C389" s="11" t="n">
+        <v>93</v>
       </c>
     </row>
     <row r="390" ht="11" customHeight="true" outlineLevel="3">
       <c r="B390" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="C390" s="11" t="n">
-        <v>194</v>
+      <c r="C390" s="18" t="n">
+        <v>3128</v>
       </c>
     </row>
     <row r="391" ht="11" customHeight="true" outlineLevel="3">
       <c r="B391" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="C391" s="18" t="n">
-        <v>5686</v>
+      <c r="C391" s="11" t="n">
+        <v>242</v>
       </c>
     </row>
     <row r="392" ht="22" customHeight="true" outlineLevel="3">
       <c r="B392" s="17" t="s">
         <v>391</v>
       </c>
-      <c r="C392" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="393" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B393" s="16" t="s">
+      <c r="C392" s="18" t="n">
+        <v>5233</v>
+      </c>
+    </row>
+    <row r="393" ht="22" customHeight="true" outlineLevel="3">
+      <c r="B393" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="C393" s="14" t="n">
-        <v>-44</v>
+      <c r="C393" s="11" t="n">
+        <v>618</v>
       </c>
     </row>
     <row r="394" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B394" s="19" t="s">
+      <c r="B394" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="C394" s="14" t="n">
-        <v>-44</v>
-      </c>
-    </row>
-    <row r="395" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B395" s="20" t="s">
+      <c r="C394" s="11" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="395" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B395" s="17" t="s">
         <v>394</v>
       </c>
       <c r="C395" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="396" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B396" s="20" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="396" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B396" s="17" t="s">
         <v>395</v>
       </c>
-      <c r="C396" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="397" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B397" s="20" t="s">
+      <c r="C396" s="18" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="397" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B397" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="C397" s="11" t="n">
-        <v>-65</v>
-      </c>
-    </row>
-    <row r="398" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B398" s="16" t="s">
+      <c r="C397" s="18" t="n">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="398" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B398" s="17" t="s">
         <v>397</v>
       </c>
-      <c r="C398" s="12" t="n">
-        <v>72498</v>
-      </c>
-    </row>
-    <row r="399" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C398" s="11" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="399" ht="22" customHeight="true" outlineLevel="3">
       <c r="B399" s="17" t="s">
         <v>398</v>
       </c>
-      <c r="C399" s="18" t="n">
-        <v>4048</v>
-      </c>
-    </row>
-    <row r="400" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C399" s="11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="400" ht="22" customHeight="true" outlineLevel="3">
       <c r="B400" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="C400" s="18" t="n">
-        <v>2167</v>
-      </c>
-    </row>
-    <row r="401" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C400" s="11" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="401" ht="22" customHeight="true" outlineLevel="3">
       <c r="B401" s="17" t="s">
         <v>400</v>
       </c>
-      <c r="C401" s="18" t="n">
-        <v>1699</v>
+      <c r="C401" s="11" t="n">
+        <v>168</v>
       </c>
     </row>
     <row r="402" ht="22" customHeight="true" outlineLevel="3">
@@ -5121,135 +4815,135 @@
         <v>401</v>
       </c>
       <c r="C402" s="11" t="n">
-        <v>341</v>
+        <v>961</v>
       </c>
     </row>
     <row r="403" ht="22" customHeight="true" outlineLevel="3">
       <c r="B403" s="17" t="s">
         <v>402</v>
       </c>
-      <c r="C403" s="18" t="n">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="404" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C403" s="11" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="404" ht="22" customHeight="true" outlineLevel="3">
       <c r="B404" s="17" t="s">
         <v>403</v>
       </c>
-      <c r="C404" s="18" t="n">
-        <v>4382</v>
-      </c>
-    </row>
-    <row r="405" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C404" s="11" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="405" ht="22" customHeight="true" outlineLevel="3">
       <c r="B405" s="17" t="s">
         <v>404</v>
       </c>
-      <c r="C405" s="18" t="n">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="406" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C405" s="11" t="n">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="406" ht="22" customHeight="true" outlineLevel="3">
       <c r="B406" s="17" t="s">
         <v>405</v>
       </c>
-      <c r="C406" s="18" t="n">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="407" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C406" s="11" t="n">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="407" ht="22" customHeight="true" outlineLevel="3">
       <c r="B407" s="17" t="s">
         <v>406</v>
       </c>
       <c r="C407" s="11" t="n">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="408" ht="11" customHeight="true" outlineLevel="3">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="408" ht="22" customHeight="true" outlineLevel="3">
       <c r="B408" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="C408" s="11" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="409" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C408" s="18" t="n">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="409" ht="22" customHeight="true" outlineLevel="3">
       <c r="B409" s="17" t="s">
         <v>408</v>
       </c>
       <c r="C409" s="11" t="n">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="410" ht="11" customHeight="true" outlineLevel="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="410" ht="22" customHeight="true" outlineLevel="3">
       <c r="B410" s="17" t="s">
         <v>409</v>
       </c>
       <c r="C410" s="11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="411" ht="11" customHeight="true" outlineLevel="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="411" ht="22" customHeight="true" outlineLevel="3">
       <c r="B411" s="17" t="s">
         <v>410</v>
       </c>
       <c r="C411" s="11" t="n">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="412" ht="11" customHeight="true" outlineLevel="3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="412" ht="22" customHeight="true" outlineLevel="3">
       <c r="B412" s="17" t="s">
         <v>411</v>
       </c>
       <c r="C412" s="11" t="n">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="413" ht="11" customHeight="true" outlineLevel="3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="413" ht="22" customHeight="true" outlineLevel="3">
       <c r="B413" s="17" t="s">
         <v>412</v>
       </c>
       <c r="C413" s="11" t="n">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="414" ht="11" customHeight="true" outlineLevel="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="414" ht="22" customHeight="true" outlineLevel="3">
       <c r="B414" s="17" t="s">
         <v>413</v>
       </c>
       <c r="C414" s="18" t="n">
-        <v>1825</v>
-      </c>
-    </row>
-    <row r="415" ht="11" customHeight="true" outlineLevel="3">
+        <v>3797</v>
+      </c>
+    </row>
+    <row r="415" ht="22" customHeight="true" outlineLevel="3">
       <c r="B415" s="17" t="s">
         <v>414</v>
       </c>
       <c r="C415" s="11" t="n">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="416" ht="11" customHeight="true" outlineLevel="3">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="416" ht="22" customHeight="true" outlineLevel="3">
       <c r="B416" s="17" t="s">
         <v>415</v>
       </c>
       <c r="C416" s="11" t="n">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="417" ht="11" customHeight="true" outlineLevel="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="417" ht="22" customHeight="true" outlineLevel="3">
       <c r="B417" s="17" t="s">
         <v>416</v>
       </c>
       <c r="C417" s="11" t="n">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="418" ht="11" customHeight="true" outlineLevel="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="418" ht="22" customHeight="true" outlineLevel="3">
       <c r="B418" s="17" t="s">
         <v>417</v>
       </c>
-      <c r="C418" s="18" t="n">
-        <v>2227</v>
+      <c r="C418" s="11" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="419" ht="11" customHeight="true" outlineLevel="3">
@@ -5257,119 +4951,119 @@
         <v>418</v>
       </c>
       <c r="C419" s="11" t="n">
-        <v>438</v>
+        <v>66</v>
       </c>
     </row>
     <row r="420" ht="11" customHeight="true" outlineLevel="3">
       <c r="B420" s="17" t="s">
         <v>419</v>
       </c>
-      <c r="C420" s="18" t="n">
-        <v>2717</v>
-      </c>
-    </row>
-    <row r="421" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C420" s="11" t="n">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="421" ht="22" customHeight="true" outlineLevel="3">
       <c r="B421" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="C421" s="18" t="n">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="422" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C421" s="11" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="422" ht="22" customHeight="true" outlineLevel="3">
       <c r="B422" s="17" t="s">
         <v>421</v>
       </c>
-      <c r="C422" s="18" t="n">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="423" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C422" s="11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="423" ht="22" customHeight="true" outlineLevel="3">
       <c r="B423" s="17" t="s">
         <v>422</v>
       </c>
-      <c r="C423" s="11" t="n">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="424" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C423" s="18" t="n">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="424" ht="22" customHeight="true" outlineLevel="3">
       <c r="B424" s="17" t="s">
         <v>423</v>
       </c>
-      <c r="C424" s="18" t="n">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="425" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C424" s="11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="425" ht="22" customHeight="true" outlineLevel="3">
       <c r="B425" s="17" t="s">
         <v>424</v>
       </c>
       <c r="C425" s="11" t="n">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="426" ht="11" customHeight="true" outlineLevel="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="426" ht="22" customHeight="true" outlineLevel="3">
       <c r="B426" s="17" t="s">
         <v>425</v>
       </c>
       <c r="C426" s="11" t="n">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="427" ht="11" customHeight="true" outlineLevel="3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="427" ht="22" customHeight="true" outlineLevel="3">
       <c r="B427" s="17" t="s">
         <v>426</v>
       </c>
       <c r="C427" s="11" t="n">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="428" ht="11" customHeight="true" outlineLevel="3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="428" ht="22" customHeight="true" outlineLevel="3">
       <c r="B428" s="17" t="s">
         <v>427</v>
       </c>
-      <c r="C428" s="11" t="n">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="429" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C428" s="18" t="n">
+        <v>3914</v>
+      </c>
+    </row>
+    <row r="429" ht="22" customHeight="true" outlineLevel="3">
       <c r="B429" s="17" t="s">
         <v>428</v>
       </c>
       <c r="C429" s="11" t="n">
-        <v>466</v>
+        <v>7</v>
       </c>
     </row>
     <row r="430" ht="11" customHeight="true" outlineLevel="3">
       <c r="B430" s="17" t="s">
         <v>429</v>
       </c>
-      <c r="C430" s="11" t="n">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="431" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C430" s="18" t="n">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="431" ht="22" customHeight="true" outlineLevel="3">
       <c r="B431" s="17" t="s">
         <v>430</v>
       </c>
       <c r="C431" s="11" t="n">
-        <v>534</v>
+        <v>500</v>
       </c>
     </row>
     <row r="432" ht="11" customHeight="true" outlineLevel="3">
       <c r="B432" s="17" t="s">
         <v>431</v>
       </c>
-      <c r="C432" s="18" t="n">
-        <v>16048</v>
-      </c>
-    </row>
-    <row r="433" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C432" s="11" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="433" ht="22" customHeight="true" outlineLevel="3">
       <c r="B433" s="17" t="s">
         <v>432</v>
       </c>
       <c r="C433" s="11" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="434" ht="11" customHeight="true" outlineLevel="3">
@@ -5377,23 +5071,23 @@
         <v>433</v>
       </c>
       <c r="C434" s="18" t="n">
-        <v>3752</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="435" ht="11" customHeight="true" outlineLevel="3">
       <c r="B435" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="C435" s="18" t="n">
-        <v>9301</v>
+      <c r="C435" s="11" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="436" ht="11" customHeight="true" outlineLevel="3">
       <c r="B436" s="17" t="s">
         <v>435</v>
       </c>
-      <c r="C436" s="18" t="n">
-        <v>1564</v>
+      <c r="C436" s="11" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="437" ht="11" customHeight="true" outlineLevel="3">
@@ -5401,47 +5095,47 @@
         <v>436</v>
       </c>
       <c r="C437" s="11" t="n">
-        <v>608</v>
+        <v>60</v>
       </c>
     </row>
     <row r="438" ht="11" customHeight="true" outlineLevel="3">
       <c r="B438" s="17" t="s">
         <v>437</v>
       </c>
-      <c r="C438" s="11" t="n">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="439" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C438" s="18" t="n">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="439" ht="22" customHeight="true" outlineLevel="3">
       <c r="B439" s="17" t="s">
         <v>438</v>
       </c>
-      <c r="C439" s="18" t="n">
-        <v>1740</v>
-      </c>
-    </row>
-    <row r="440" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C439" s="11" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="440" ht="22" customHeight="true" outlineLevel="3">
       <c r="B440" s="17" t="s">
         <v>439</v>
       </c>
       <c r="C440" s="11" t="n">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="441" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B441" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="441" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B441" s="17" t="s">
         <v>440</v>
       </c>
-      <c r="C441" s="14" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="442" ht="11" customHeight="true" outlineLevel="3">
+      <c r="C441" s="18" t="n">
+        <v>4385</v>
+      </c>
+    </row>
+    <row r="442" ht="22" customHeight="true" outlineLevel="3">
       <c r="B442" s="17" t="s">
         <v>441</v>
       </c>
       <c r="C442" s="11" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
     </row>
     <row r="443" ht="11" customHeight="true" outlineLevel="3">
@@ -5449,23 +5143,23 @@
         <v>442</v>
       </c>
       <c r="C443" s="11" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="444" ht="11" customHeight="true" outlineLevel="3">
       <c r="B444" s="17" t="s">
         <v>443</v>
       </c>
-      <c r="C444" s="11" t="n">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="445" ht="11" customHeight="true" outlineLevel="2">
-      <c r="B445" s="16" t="s">
+      <c r="C444" s="18" t="n">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="445" ht="11" customHeight="true" outlineLevel="3">
+      <c r="B445" s="17" t="s">
         <v>444</v>
       </c>
-      <c r="C445" s="12" t="n">
-        <v>77376</v>
+      <c r="C445" s="11" t="n">
+        <v>624</v>
       </c>
     </row>
     <row r="446" ht="11" customHeight="true" outlineLevel="3">
@@ -5473,7 +5167,7 @@
         <v>445</v>
       </c>
       <c r="C446" s="11" t="n">
-        <v>402</v>
+        <v>904</v>
       </c>
     </row>
     <row r="447" ht="11" customHeight="true" outlineLevel="3">
@@ -5481,15 +5175,15 @@
         <v>446</v>
       </c>
       <c r="C447" s="11" t="n">
-        <v>3</v>
+        <v>642</v>
       </c>
     </row>
     <row r="448" ht="11" customHeight="true" outlineLevel="3">
       <c r="B448" s="17" t="s">
         <v>447</v>
       </c>
-      <c r="C448" s="11" t="n">
-        <v>90</v>
+      <c r="C448" s="18" t="n">
+        <v>1863</v>
       </c>
     </row>
     <row r="449" ht="11" customHeight="true" outlineLevel="3">
@@ -5497,15 +5191,15 @@
         <v>448</v>
       </c>
       <c r="C449" s="11" t="n">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="450" ht="22" customHeight="true" outlineLevel="3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="450" ht="11" customHeight="true" outlineLevel="3">
       <c r="B450" s="17" t="s">
         <v>449</v>
       </c>
-      <c r="C450" s="11" t="n">
-        <v>272</v>
+      <c r="C450" s="18" t="n">
+        <v>3946</v>
       </c>
     </row>
     <row r="451" ht="22" customHeight="true" outlineLevel="3">
@@ -5513,815 +5207,15 @@
         <v>450</v>
       </c>
       <c r="C451" s="11" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="452" ht="22" customHeight="true" outlineLevel="3">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="452" ht="11" customHeight="true" outlineLevel="3">
       <c r="B452" s="17" t="s">
         <v>451</v>
       </c>
-      <c r="C452" s="11" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="453" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B453" s="17" t="s">
-        <v>452</v>
-      </c>
-      <c r="C453" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="454" ht="33" customHeight="true" outlineLevel="3">
-      <c r="B454" s="17" t="s">
-        <v>453</v>
-      </c>
-      <c r="C454" s="18" t="n">
-        <v>5647</v>
-      </c>
-    </row>
-    <row r="455" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B455" s="17" t="s">
-        <v>454</v>
-      </c>
-      <c r="C455" s="11" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="456" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B456" s="17" t="s">
-        <v>455</v>
-      </c>
-      <c r="C456" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="457" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B457" s="17" t="s">
-        <v>456</v>
-      </c>
-      <c r="C457" s="11" t="n">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="458" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B458" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="C458" s="11" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="459" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B459" s="17" t="s">
-        <v>458</v>
-      </c>
-      <c r="C459" s="11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="460" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B460" s="17" t="s">
-        <v>459</v>
-      </c>
-      <c r="C460" s="18" t="n">
-        <v>1676</v>
-      </c>
-    </row>
-    <row r="461" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B461" s="17" t="s">
-        <v>460</v>
-      </c>
-      <c r="C461" s="11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="462" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B462" s="17" t="s">
-        <v>461</v>
-      </c>
-      <c r="C462" s="11" t="n">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="463" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B463" s="17" t="s">
-        <v>462</v>
-      </c>
-      <c r="C463" s="11" t="n">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="464" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B464" s="17" t="s">
-        <v>463</v>
-      </c>
-      <c r="C464" s="18" t="n">
-        <v>3289</v>
-      </c>
-    </row>
-    <row r="465" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B465" s="17" t="s">
-        <v>464</v>
-      </c>
-      <c r="C465" s="11" t="n">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="466" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B466" s="17" t="s">
-        <v>465</v>
-      </c>
-      <c r="C466" s="11" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="467" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B467" s="17" t="s">
-        <v>466</v>
-      </c>
-      <c r="C467" s="18" t="n">
-        <v>6662</v>
-      </c>
-    </row>
-    <row r="468" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B468" s="17" t="s">
-        <v>467</v>
-      </c>
-      <c r="C468" s="11" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="469" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B469" s="17" t="s">
-        <v>468</v>
-      </c>
-      <c r="C469" s="11" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="470" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B470" s="17" t="s">
-        <v>469</v>
-      </c>
-      <c r="C470" s="11" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="471" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B471" s="17" t="s">
-        <v>470</v>
-      </c>
-      <c r="C471" s="11" t="n">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="472" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B472" s="17" t="s">
-        <v>471</v>
-      </c>
-      <c r="C472" s="11" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="473" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B473" s="17" t="s">
-        <v>472</v>
-      </c>
-      <c r="C473" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="474" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B474" s="17" t="s">
-        <v>473</v>
-      </c>
-      <c r="C474" s="11" t="n">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="475" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B475" s="17" t="s">
-        <v>474</v>
-      </c>
-      <c r="C475" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="476" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B476" s="17" t="s">
-        <v>475</v>
-      </c>
-      <c r="C476" s="11" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="477" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B477" s="17" t="s">
-        <v>476</v>
-      </c>
-      <c r="C477" s="11" t="n">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="478" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B478" s="17" t="s">
-        <v>477</v>
-      </c>
-      <c r="C478" s="18" t="n">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="479" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B479" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="C479" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="480" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B480" s="17" t="s">
-        <v>479</v>
-      </c>
-      <c r="C480" s="11" t="n">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="481" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B481" s="17" t="s">
-        <v>480</v>
-      </c>
-      <c r="C481" s="11" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="482" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B482" s="17" t="s">
-        <v>481</v>
-      </c>
-      <c r="C482" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="483" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B483" s="17" t="s">
-        <v>482</v>
-      </c>
-      <c r="C483" s="18" t="n">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="484" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B484" s="17" t="s">
-        <v>483</v>
-      </c>
-      <c r="C484" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="485" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B485" s="17" t="s">
-        <v>484</v>
-      </c>
-      <c r="C485" s="11" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="486" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B486" s="17" t="s">
-        <v>485</v>
-      </c>
-      <c r="C486" s="11" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="487" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B487" s="17" t="s">
-        <v>486</v>
-      </c>
-      <c r="C487" s="11" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="488" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B488" s="17" t="s">
-        <v>487</v>
-      </c>
-      <c r="C488" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="489" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B489" s="17" t="s">
-        <v>488</v>
-      </c>
-      <c r="C489" s="11" t="n">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="490" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B490" s="17" t="s">
-        <v>489</v>
-      </c>
-      <c r="C490" s="11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="491" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B491" s="17" t="s">
-        <v>490</v>
-      </c>
-      <c r="C491" s="11" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="492" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B492" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="C492" s="18" t="n">
-        <v>2112</v>
-      </c>
-    </row>
-    <row r="493" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B493" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="C493" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="494" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B494" s="17" t="s">
-        <v>493</v>
-      </c>
-      <c r="C494" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="495" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B495" s="17" t="s">
-        <v>494</v>
-      </c>
-      <c r="C495" s="11" t="n">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="496" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B496" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="C496" s="11" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="497" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B497" s="17" t="s">
-        <v>496</v>
-      </c>
-      <c r="C497" s="11" t="n">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="498" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B498" s="17" t="s">
-        <v>497</v>
-      </c>
-      <c r="C498" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="499" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B499" s="17" t="s">
-        <v>498</v>
-      </c>
-      <c r="C499" s="11" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="500" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B500" s="17" t="s">
-        <v>499</v>
-      </c>
-      <c r="C500" s="11" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="501" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B501" s="17" t="s">
-        <v>500</v>
-      </c>
-      <c r="C501" s="11" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="502" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B502" s="17" t="s">
-        <v>501</v>
-      </c>
-      <c r="C502" s="11" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="503" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B503" s="17" t="s">
-        <v>502</v>
-      </c>
-      <c r="C503" s="11" t="n">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="504" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B504" s="17" t="s">
-        <v>503</v>
-      </c>
-      <c r="C504" s="11" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="505" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B505" s="17" t="s">
-        <v>504</v>
-      </c>
-      <c r="C505" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="506" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B506" s="17" t="s">
-        <v>505</v>
-      </c>
-      <c r="C506" s="11" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="507" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B507" s="17" t="s">
-        <v>506</v>
-      </c>
-      <c r="C507" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="508" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B508" s="17" t="s">
-        <v>507</v>
-      </c>
-      <c r="C508" s="11" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="509" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B509" s="17" t="s">
-        <v>508</v>
-      </c>
-      <c r="C509" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="510" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B510" s="17" t="s">
-        <v>509</v>
-      </c>
-      <c r="C510" s="11" t="n">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="511" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B511" s="17" t="s">
-        <v>510</v>
-      </c>
-      <c r="C511" s="11" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="512" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B512" s="17" t="s">
-        <v>511</v>
-      </c>
-      <c r="C512" s="11" t="n">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="513" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B513" s="17" t="s">
-        <v>512</v>
-      </c>
-      <c r="C513" s="11" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="514" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B514" s="17" t="s">
-        <v>513</v>
-      </c>
-      <c r="C514" s="18" t="n">
-        <v>2907</v>
-      </c>
-    </row>
-    <row r="515" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B515" s="17" t="s">
-        <v>514</v>
-      </c>
-      <c r="C515" s="11" t="n">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="516" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B516" s="17" t="s">
-        <v>515</v>
-      </c>
-      <c r="C516" s="11" t="n">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="517" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B517" s="17" t="s">
-        <v>516</v>
-      </c>
-      <c r="C517" s="11" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="518" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B518" s="17" t="s">
-        <v>517</v>
-      </c>
-      <c r="C518" s="11" t="n">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="519" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B519" s="17" t="s">
-        <v>518</v>
-      </c>
-      <c r="C519" s="11" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="520" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B520" s="17" t="s">
-        <v>519</v>
-      </c>
-      <c r="C520" s="11" t="n">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="521" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B521" s="17" t="s">
-        <v>520</v>
-      </c>
-      <c r="C521" s="11" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="522" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B522" s="17" t="s">
-        <v>521</v>
-      </c>
-      <c r="C522" s="11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="523" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B523" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="C523" s="18" t="n">
-        <v>9759</v>
-      </c>
-    </row>
-    <row r="524" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B524" s="17" t="s">
-        <v>523</v>
-      </c>
-      <c r="C524" s="11" t="n">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="525" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B525" s="17" t="s">
-        <v>524</v>
-      </c>
-      <c r="C525" s="11" t="n">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="526" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B526" s="17" t="s">
-        <v>525</v>
-      </c>
-      <c r="C526" s="18" t="n">
-        <v>3215</v>
-      </c>
-    </row>
-    <row r="527" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B527" s="17" t="s">
-        <v>526</v>
-      </c>
-      <c r="C527" s="11" t="n">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="528" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B528" s="17" t="s">
-        <v>527</v>
-      </c>
-      <c r="C528" s="11" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="529" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B529" s="17" t="s">
-        <v>528</v>
-      </c>
-      <c r="C529" s="18" t="n">
-        <v>2646</v>
-      </c>
-    </row>
-    <row r="530" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B530" s="17" t="s">
-        <v>529</v>
-      </c>
-      <c r="C530" s="11" t="n">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="531" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B531" s="17" t="s">
-        <v>530</v>
-      </c>
-      <c r="C531" s="11" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="532" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B532" s="17" t="s">
-        <v>531</v>
-      </c>
-      <c r="C532" s="18" t="n">
-        <v>3539</v>
-      </c>
-    </row>
-    <row r="533" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B533" s="17" t="s">
-        <v>532</v>
-      </c>
-      <c r="C533" s="18" t="n">
-        <v>1417</v>
-      </c>
-    </row>
-    <row r="534" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B534" s="17" t="s">
-        <v>533</v>
-      </c>
-      <c r="C534" s="11" t="n">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="535" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B535" s="17" t="s">
-        <v>534</v>
-      </c>
-      <c r="C535" s="11" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="536" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B536" s="17" t="s">
-        <v>535</v>
-      </c>
-      <c r="C536" s="18" t="n">
-        <v>1840</v>
-      </c>
-    </row>
-    <row r="537" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B537" s="17" t="s">
-        <v>536</v>
-      </c>
-      <c r="C537" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="538" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B538" s="17" t="s">
-        <v>537</v>
-      </c>
-      <c r="C538" s="11" t="n">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="539" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B539" s="17" t="s">
-        <v>538</v>
-      </c>
-      <c r="C539" s="11" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="540" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B540" s="17" t="s">
-        <v>539</v>
-      </c>
-      <c r="C540" s="11" t="n">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="541" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B541" s="17" t="s">
-        <v>540</v>
-      </c>
-      <c r="C541" s="18" t="n">
-        <v>3586</v>
-      </c>
-    </row>
-    <row r="542" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B542" s="17" t="s">
-        <v>541</v>
-      </c>
-      <c r="C542" s="11" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="543" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B543" s="17" t="s">
-        <v>542</v>
-      </c>
-      <c r="C543" s="18" t="n">
-        <v>1983</v>
-      </c>
-    </row>
-    <row r="544" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B544" s="17" t="s">
-        <v>543</v>
-      </c>
-      <c r="C544" s="11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="545" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B545" s="17" t="s">
-        <v>544</v>
-      </c>
-      <c r="C545" s="18" t="n">
-        <v>2772</v>
-      </c>
-    </row>
-    <row r="546" ht="22" customHeight="true" outlineLevel="3">
-      <c r="B546" s="17" t="s">
-        <v>545</v>
-      </c>
-      <c r="C546" s="11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="547" ht="11" customHeight="true" outlineLevel="3">
-      <c r="B547" s="19" t="s">
-        <v>546</v>
-      </c>
-      <c r="C547" s="12" t="n">
-        <v>7322</v>
-      </c>
-    </row>
-    <row r="548" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B548" s="20" t="s">
-        <v>547</v>
-      </c>
-      <c r="C548" s="18" t="n">
-        <v>2151</v>
-      </c>
-    </row>
-    <row r="549" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B549" s="20" t="s">
-        <v>548</v>
-      </c>
-      <c r="C549" s="11" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="550" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B550" s="20" t="s">
-        <v>549</v>
-      </c>
-      <c r="C550" s="18" t="n">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="551" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B551" s="20" t="s">
-        <v>550</v>
-      </c>
-      <c r="C551" s="18" t="n">
-        <v>4104</v>
-      </c>
-    </row>
-    <row r="552" ht="11" customHeight="true" outlineLevel="4">
-      <c r="B552" s="20" t="s">
-        <v>551</v>
-      </c>
-      <c r="C552" s="11" t="n">
-        <v>40</v>
+      <c r="C452" s="18" t="n">
+        <v>1828</v>
       </c>
     </row>
   </sheetData>
